--- a/ios/localizzazione/NEAT_testi_tradotti.xlsx
+++ b/ios/localizzazione/NEAT_testi_tradotti.xlsx
@@ -1473,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13387,7 +13387,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>set.info.section</t>
+          <t>set.backup.section</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -13402,74 +13402,74 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Titolo di sezione.</t>
+          <t>Titolo di sezione: copia manuale dei dati dell'app in un file.</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>≤ 20</t>
+          <t>≤ 24</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Informazioni</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Copia de seguridad</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>Informations</t>
+          <t>Sauvegarde</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>Informationen</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="K146" s="6" t="inlineStr">
         <is>
-          <t>Informações</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr">
         <is>
-          <t>情報</t>
+          <t>バックアップ</t>
         </is>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
-          <t>정보</t>
+          <t>백업</t>
         </is>
       </c>
       <c r="N146" s="6" t="inlineStr">
         <is>
-          <t>信息</t>
+          <t>备份</t>
         </is>
       </c>
       <c r="O146" s="6" t="inlineStr">
         <is>
-          <t>資訊</t>
+          <t>備份</t>
         </is>
       </c>
       <c r="P146" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>set.info.privacy</t>
+          <t>set.backup.export</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -13484,74 +13484,74 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Riga che apre la pagina web della privacy.</t>
+          <t>Riga che apre il foglio di condivisione per salvare il file di backup (File, AirDrop, Mail…).</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>≤ 20</t>
+          <t>≤ 28</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Esporta backup</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Export backup</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>Privacidad</t>
+          <t>Exportar copia</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>Confidentialité</t>
+          <t>Exporter la sauvegarde</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Datenschutz</t>
+          <t>Backup exportieren</t>
         </is>
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>Privacidade</t>
+          <t>Exportar backup</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr">
         <is>
-          <t>プライバシー</t>
+          <t>バックアップを書き出す</t>
         </is>
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
-          <t>개인정보 보호</t>
+          <t>백업 내보내기</t>
         </is>
       </c>
       <c r="N147" s="6" t="inlineStr">
         <is>
-          <t>隐私</t>
+          <t>导出备份</t>
         </is>
       </c>
       <c r="O147" s="6" t="inlineStr">
         <is>
-          <t>隱私權</t>
+          <t>匯出備份</t>
         </is>
       </c>
       <c r="P147" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>set.info.support</t>
+          <t>set.backup.import</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -13566,74 +13566,74 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Riga che apre la pagina web di supporto.</t>
+          <t>Riga che apre la scelta di un file di backup da importare.</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>≤ 20</t>
+          <t>≤ 28</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Supporto</t>
+          <t>Importa backup</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Import backup</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Importar copia</t>
         </is>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>Assistance</t>
+          <t>Importer une sauvegarde</t>
         </is>
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Backup importieren</t>
         </is>
       </c>
       <c r="K148" s="6" t="inlineStr">
         <is>
-          <t>Suporte</t>
+          <t>Importar backup</t>
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr">
         <is>
-          <t>サポート</t>
+          <t>バックアップを読み込む</t>
         </is>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
-          <t>지원</t>
+          <t>백업 가져오기</t>
         </is>
       </c>
       <c r="N148" s="6" t="inlineStr">
         <is>
-          <t>支持</t>
+          <t>导入备份</t>
         </is>
       </c>
       <c r="O148" s="6" t="inlineStr">
         <is>
-          <t>支援</t>
+          <t>匯入備份</t>
         </is>
       </c>
       <c r="P148" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>set.info.intro</t>
+          <t>set.backup.note</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -13648,74 +13648,70 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Riga che mostra di nuovo l'introduzione.</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>≤ 28</t>
-        </is>
-      </c>
+          <t>Nota sotto il backup: cosa contiene il file, che i passi restano in Salute e che c'è anche la copia automatica in iCloud.</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Rivedi l'introduzione</t>
+          <t>Un file con inizio della streak, storico degli obiettivi e impostazioni, da salvare dove vuoi. I passi non ci sono: restano in Salute. Se usi iCloud, una copia si salva anche lì da sola.</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>Replay introduction</t>
+          <t>A file with your streak start, goal history and settings, to save wherever you like. Steps aren't included: they stay in Health. If you use iCloud, a copy is also saved there automatically.</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>Repetir la introducción</t>
+          <t>Un archivo con el inicio de tu racha, el historial de objetivos y los ajustes, para guardarlo donde quieras. Los pasos no se incluyen: se quedan en Salud. Si usas iCloud, también se guarda una copia allí automáticamente.</t>
         </is>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>Revoir l’introduction</t>
+          <t>Un fichier avec le début de ta série, l’historique des objectifs et les réglages, à enregistrer où tu veux. Les pas n’y sont pas : ils restent dans Santé. Si tu utilises iCloud, une copie y est aussi enregistrée automatiquement.</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Einführung erneut ansehen</t>
+          <t>Eine Datei mit dem Start deiner Serie, dem Zielverlauf und den Einstellungen. Speichere sie, wo du willst. Schritte sind nicht enthalten: Sie bleiben in Health. Wenn du iCloud nutzt, wird dort automatisch auch eine Kopie gespeichert.</t>
         </is>
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>Rever a introdução</t>
+          <t>Um arquivo com o início da sua sequência, o histórico de metas e os ajustes, para salvar onde quiser. Os passos não entram: ficam no Saúde. Se você usa o iCloud, uma cópia também é salva lá automaticamente.</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr">
         <is>
-          <t>はじめの説明をもう一度見る</t>
+          <t>連続記録の開始日、目標の履歴、設定をまとめたファイルです。好きな場所に保存できます。歩数は含まれず、ヘルスケアに残ります。iCloudを使っている場合は、iCloudにも自動でコピーが保存されます。</t>
         </is>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
-          <t>시작 안내 다시 보기</t>
+          <t>연속 기록 시작일, 목표 기록, 설정이 담긴 파일로 원하는 곳에 저장할 수 있어요. 걸음 수는 포함되지 않고 건강 앱에 그대로 남아요. iCloud를 사용하면 iCloud에도 사본이 자동으로 저장돼요.</t>
         </is>
       </c>
       <c r="N149" s="6" t="inlineStr">
         <is>
-          <t>重看介绍</t>
+          <t>包含连续记录开始日期、目标历史和设置的文件，可保存到任意位置。步数不包含在内，仍保留在“健康”中。如果你使用 iCloud，副本也会自动保存在 iCloud 中。</t>
         </is>
       </c>
       <c r="O149" s="6" t="inlineStr">
         <is>
-          <t>重看介紹</t>
+          <t>包含連續紀錄開始日期、目標歷史和設定的檔案，可儲存到任何位置。步數不包含在內，仍保留在「健康」中。如果你使用 iCloud，副本也會自動儲存在 iCloud 中。</t>
         </is>
       </c>
       <c r="P149" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="72" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>set.version</t>
+          <t>set.backup.confirm.title</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -13730,79 +13726,79 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Nota in fondo. {versione} = es. 1.0.</t>
+          <t>Titolo dell'avviso di conferma prima di importare.</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>≤ 16</t>
+          <t>≤ 32</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Versione {versione}</t>
+          <t>Importare il backup?</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Version {versione}</t>
+          <t>Import backup?</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>Versión {versione}</t>
+          <t>¿Importar la copia?</t>
         </is>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>Version {versione}</t>
+          <t>Importer la sauvegarde ?</t>
         </is>
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>Version {versione}</t>
+          <t>Backup importieren?</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>Versão {versione}</t>
+          <t>Importar backup?</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr">
         <is>
-          <t>バージョン {versione}</t>
+          <t>バックアップを読み込みますか？</t>
         </is>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
-          <t>버전 {versione}</t>
+          <t>백업을 가져올까요?</t>
         </is>
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
-          <t>版本 {versione}</t>
+          <t>导入备份？</t>
         </is>
       </c>
       <c r="O150" s="6" t="inlineStr">
         <is>
-          <t>版本 {versione}</t>
+          <t>匯入備份？</t>
         </is>
       </c>
       <c r="P150" s="6" t="inlineStr">
         <is>
-          <t>Conteggio letterale: EN 18/16, ES 18/16, FR 18/16, DE 18/16, PT-BR 17/16. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 11/16, ES 11/16, FR 11/16, DE 11/16, PT-BR 10/16. Verificare anche numeri più lunghi nella build.</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>party.title</t>
+          <t>set.backup.confirm.body</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
@@ -13812,79 +13808,75 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Schermata a tutto schermo quando chiudi l'obiettivo. Titolo gigante, MAIUSCOLO.</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>≤ 20</t>
-        </is>
-      </c>
+          <t>Testo dell'avviso di conferma. {data} = data del backup nel formato della lingua (es. 22 ottobre 2026).</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>OBIETTIVO RAGGIUNTO!</t>
+          <t>Obiettivi e impostazioni verranno sostituiti con quelli del backup ({data}). La streak non si accorcia.</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>GOAL REACHED!</t>
+          <t>Your goals and settings will be replaced with those from the {data} backup. Your streak won't get shorter.</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>¡OBJETIVO ALCANZADO!</t>
+          <t>Tus objetivos y ajustes se sustituirán por los de la copia del {data}. Tu racha no se acortará.</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>OBJECTIF ATTEINT !</t>
+          <t>Tes objectifs et réglages seront remplacés par ceux de la sauvegarde du {data}. Ta série ne raccourcira pas.</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>ZIEL ERREICHT!</t>
+          <t>Deine Ziele und Einstellungen werden durch die aus dem Backup vom {data} ersetzt. Deine Serie wird nicht kürzer.</t>
         </is>
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>META ATINGIDA!</t>
+          <t>Suas metas e ajustes serão substituídos pelos do backup de {data}. Sua sequência não vai diminuir.</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
-          <t>目標達成！</t>
+          <t>目標と設定が{data}のバックアップの内容に置き換わります。連続記録が短くなることはありません。</t>
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
-          <t>목표 달성!</t>
+          <t>목표와 설정이 {data} 백업의 내용으로 바뀌어요. 연속 기록은 줄어들지 않아요.</t>
         </is>
       </c>
       <c r="N151" s="6" t="inlineStr">
         <is>
-          <t>目标达成！</t>
+          <t>目标和设置将替换为 {data} 备份中的内容。连续记录不会缩短。</t>
         </is>
       </c>
       <c r="O151" s="6" t="inlineStr">
         <is>
-          <t>目標達成！</t>
+          <t>目標和設定將替換為 {data} 備份中的內容。連續紀錄不會縮短。</t>
         </is>
       </c>
       <c r="P151" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="120" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>party.of</t>
+          <t>set.backup.confirm.ok</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -13894,79 +13886,79 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Sotto il numero dei passi. {obiettivo} = numero.</t>
+          <t>Bottone dell'avviso che conferma l'importazione.</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>≤ 18</t>
+          <t>≤ 14</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>PASSI SU {obiettivo}</t>
+          <t>Importa</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>OF {obiettivo} STEPS</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>PASOS DE {obiettivo}</t>
+          <t>Importar</t>
         </is>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>PAS SUR {obiettivo}</t>
+          <t>Importer</t>
         </is>
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>VON {obiettivo} SCHR.</t>
+          <t>Importieren</t>
         </is>
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>PASSOS DE {obiettivo}</t>
+          <t>Importar</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr">
         <is>
-          <t>目標 {obiettivo}歩</t>
+          <t>読み込む</t>
         </is>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
-          <t>목표 {obiettivo}걸음</t>
+          <t>가져오기</t>
         </is>
       </c>
       <c r="N152" s="6" t="inlineStr">
         <is>
-          <t>目标 {obiettivo}步</t>
+          <t>导入</t>
         </is>
       </c>
       <c r="O152" s="6" t="inlineStr">
         <is>
-          <t>目標 {obiettivo}步</t>
+          <t>匯入</t>
         </is>
       </c>
       <c r="P152" s="6" t="inlineStr">
         <is>
-          <t>DE: SCHR. abbrevia l’unità per lo spazio; copre anche la flessione richiesta da VON. JA/KO/ZH: formato con obiettivo esplicito, più naturale nel blocco sotto il numero. Conteggio letterale: EN 20/18, ES 20/18, FR 19/18, DE 21/18, PT-BR 21/18. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 15/18, ES 15/18, FR 14/18, DE 16/18, PT-BR 16/18. Verificare anche numeri più lunghi nella build.</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="60" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>party.streak.one</t>
+          <t>set.backup.done</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
@@ -13976,79 +13968,75 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Riga sulla serie, singolare.</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>≤ 20</t>
-        </is>
-      </c>
+          <t>Avviso dopo l'importazione riuscita.</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>1 GIORNO DI FILA</t>
+          <t>Backup importato.</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1 DAY IN A ROW</t>
+          <t>Backup imported.</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>1 DÍA SEGUIDO</t>
+          <t>Copia importada.</t>
         </is>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>1 J. D’AFFILÉE</t>
+          <t>Sauvegarde importée.</t>
         </is>
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>1 TAG IN FOLGE</t>
+          <t>Backup importiert.</t>
         </is>
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>1 DIA SEGUIDO</t>
+          <t>Backup importado.</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr">
         <is>
-          <t>1日連続</t>
+          <t>バックアップを読み込みました。</t>
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>1일 연속</t>
+          <t>백업을 가져왔어요.</t>
         </is>
       </c>
       <c r="N153" s="6" t="inlineStr">
         <is>
-          <t>连续1天</t>
+          <t>备份已导入。</t>
         </is>
       </c>
       <c r="O153" s="6" t="inlineStr">
         <is>
-          <t>連續1天</t>
+          <t>備份已匯入。</t>
         </is>
       </c>
       <c r="P153" s="6" t="inlineStr">
         <is>
-          <t>JA/KO/ZH: la forma non cambia per il plurale; conservato 1 in .one e {n} in .other, come negli originali. FR: J. abbrevia jour, in coerenza con il plurale e con il widget più stretto.</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="60" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>party.streak.other</t>
+          <t>set.backup.error</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -14058,308 +14046,300 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Plurale. {n} = numero.</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>≤ 20</t>
-        </is>
-      </c>
+          <t>Avviso se il file scelto non è un backup di NEAT.</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>{n} GIORNI DI FILA</t>
+          <t>Questo file non è un backup di NEAT.</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>{n} DAYS IN A ROW</t>
+          <t>This file isn't a NEAT backup.</t>
         </is>
       </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>{n} DÍAS SEGUIDOS</t>
+          <t>Este archivo no es una copia de NEAT.</t>
         </is>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>{n} J. D’AFFILÉE</t>
+          <t>Ce fichier n’est pas une sauvegarde NEAT.</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>{n} TAGE IN FOLGE</t>
+          <t>Diese Datei ist kein NEAT-Backup.</t>
         </is>
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>{n} DIAS SEGUIDOS</t>
+          <t>Este arquivo não é um backup do NEAT.</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr">
         <is>
-          <t>{n}日連続</t>
+          <t>このファイルはNEATのバックアップではありません。</t>
         </is>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
-          <t>{n}일 연속</t>
+          <t>이 파일은 NEAT 백업이 아니에요.</t>
         </is>
       </c>
       <c r="N154" s="6" t="inlineStr">
         <is>
-          <t>连续{n}天</t>
+          <t>此文件不是 NEAT 备份。</t>
         </is>
       </c>
       <c r="O154" s="6" t="inlineStr">
         <is>
-          <t>連續{n}天</t>
+          <t>此檔案不是 NEAT 備份。</t>
         </is>
       </c>
       <c r="P154" s="6" t="inlineStr">
         <is>
-          <t>FR: J. abbrevia jours, per lasciare spazio anche a serie di almeno 100 giorni nel widget. Stessa resa in w.lock.streak.other per coerenza con l’italiano identico. JA/KO/ZH: nessuna flessione di plurale.</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>party.vo</t>
+          <t>set.backup.error.newer</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>{passi}, {obiettivo} = numeri.</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Avviso se il backup è stato fatto da una versione più nuova dell'app.</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n"/>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Obiettivo raggiunto: {passi} passi su {obiettivo}</t>
+          <t>Questo backup viene da una versione più nuova di NEAT. Aggiorna l'app e riprova.</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>Goal reached: {passi} steps of {obiettivo}</t>
+          <t>This backup is from a newer version of NEAT. Update the app and try again.</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>Objetivo alcanzado: {passi} pasos de {obiettivo}</t>
+          <t>Esta copia es de una versión más reciente de NEAT. Actualiza la app y vuelve a intentarlo.</t>
         </is>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>Objectif atteint : {passi} pas sur {obiettivo}</t>
+          <t>Cette sauvegarde vient d’une version plus récente de NEAT. Mets l’app à jour et réessaie.</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Ziel erreicht: {passi} Schritte von {obiettivo}</t>
+          <t>Dieses Backup stammt aus einer neueren Version von NEAT. Aktualisiere die App und versuche es erneut.</t>
         </is>
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>Meta atingida: {passi} passos de {obiettivo}</t>
+          <t>Este backup é de uma versão mais nova do NEAT. Atualize o app e tente de novo.</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr">
         <is>
-          <t>目標達成。{obiettivo}歩の目標に対し、{passi}歩です</t>
+          <t>このバックアップは新しいバージョンのNEATで作成されています。アプリをアップデートしてもう一度お試しください。</t>
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
-          <t>목표 달성. 목표 {obiettivo}걸음 중 {passi}걸음을 걸었습니다</t>
+          <t>이 백업은 더 새로운 버전의 NEAT에서 만들어졌어요. 앱을 업데이트한 후 다시 시도해 주세요.</t>
         </is>
       </c>
       <c r="N155" s="6" t="inlineStr">
         <is>
-          <t>目标达成：已走{passi}步，目标{obiettivo}步</t>
+          <t>此备份来自更新版本的 NEAT。请更新 App 后重试。</t>
         </is>
       </c>
       <c r="O155" s="6" t="inlineStr">
         <is>
-          <t>目標達成：已走{passi}步，目標{obiettivo}步</t>
+          <t>此備份來自較新版本的 NEAT。請更新 App 後再試一次。</t>
         </is>
       </c>
       <c r="P155" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>party.close.vo</t>
+          <t>set.backup.ok</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Festa obiettivo</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Suggerimento: come chiuderla.</t>
+          <t>Bottone che chiude l'avviso di esito.</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 10</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Tocca per chiudere</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>Tap to close</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>Toca para cerrar</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>Touche pour fermer</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>Zum Schließen tippen</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>Toque para fechar</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr">
         <is>
-          <t>タップして閉じる</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
-          <t>탭하여 닫기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="N156" s="6" t="inlineStr">
         <is>
-          <t>轻点以关闭</t>
+          <t>好</t>
         </is>
       </c>
       <c r="O156" s="6" t="inlineStr">
         <is>
-          <t>點一下以關閉</t>
+          <t>好</t>
         </is>
       </c>
       <c r="P156" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>w.gallery.name</t>
+          <t>set.info.section</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Nome del widget nella galleria dei widget di iOS.</t>
+          <t>Titolo di sezione.</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>≤ 24</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Passi di oggi</t>
+          <t>Informazioni</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>Today's steps</t>
+          <t>About</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>Pasos de hoy</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>Pas du jour</t>
+          <t>Informations</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Heutige Schritte</t>
+          <t>Informationen</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>Passos de hoje</t>
+          <t>Informações</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr">
         <is>
-          <t>今日の歩数</t>
+          <t>情報</t>
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>오늘 걸음 수</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="N157" s="6" t="inlineStr">
         <is>
-          <t>今日步数</t>
+          <t>信息</t>
         </is>
       </c>
       <c r="O157" s="6" t="inlineStr">
         <is>
-          <t>今日步數</t>
+          <t>資訊</t>
         </is>
       </c>
       <c r="P157" s="6" t="inlineStr">
@@ -14371,77 +14351,77 @@
     <row r="158" ht="24" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>w.gallery.desc</t>
+          <t>set.info.privacy</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Descrizione nella galleria dei widget.</t>
+          <t>Riga che apre la pagina web della privacy.</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>≤ 70</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Passi, minuti che mancano e serie, anche sul blocco schermo.</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>Steps, minutes left and your streak, even on the Lock Screen.</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>Pasos, minutos restantes y racha, también en la pantalla de bloqueo.</t>
+          <t>Privacidad</t>
         </is>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>Pas, minutes restantes et série, même sur l’écran verrouillé.</t>
+          <t>Confidentialité</t>
         </is>
       </c>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>Schritte, übrige Minuten und Serie, auch auf dem Sperrbildschirm.</t>
+          <t>Datenschutz</t>
         </is>
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>Passos, minutos restantes e sequência, até na Tela Bloqueada.</t>
+          <t>Privacidade</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr">
         <is>
-          <t>歩数、残り時間、連続記録をロック画面でもチェック。</t>
+          <t>プライバシー</t>
         </is>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
-          <t>잠금 화면에서도 걸음 수, 남은 시간, 연속 기록을 확인해요.</t>
+          <t>개인정보 보호</t>
         </is>
       </c>
       <c r="N158" s="6" t="inlineStr">
         <is>
-          <t>步数、剩余分钟数和连续记录，锁定屏幕上也能看。</t>
+          <t>隐私</t>
         </is>
       </c>
       <c r="O158" s="6" t="inlineStr">
         <is>
-          <t>步數、剩餘分鐘數和連續紀錄，鎖定畫面上也能看。</t>
+          <t>隱私權</t>
         </is>
       </c>
       <c r="P158" s="6" t="inlineStr">
@@ -14453,77 +14433,77 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>w.stepsToday</t>
+          <t>set.info.support</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Widget medio: etichetta sopra il numero dei passi, MAIUSCOLO.</t>
+          <t>Riga che apre la pagina web di supporto.</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>≤ 16</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>PASSI DI OGGI</t>
+          <t>Supporto</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>TODAY’S STEPS</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>PASOS DE HOY</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>PAS DU JOUR</t>
+          <t>Assistance</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>HEUTIGE SCHRITTE</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>PASSOS DE HOJE</t>
+          <t>Suporte</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
-          <t>今日の歩数</t>
+          <t>サポート</t>
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
-          <t>오늘 걸음 수</t>
+          <t>지원</t>
         </is>
       </c>
       <c r="N159" s="6" t="inlineStr">
         <is>
-          <t>今日步数</t>
+          <t>支持</t>
         </is>
       </c>
       <c r="O159" s="6" t="inlineStr">
         <is>
-          <t>今日步數</t>
+          <t>支援</t>
         </is>
       </c>
       <c r="P159" s="6" t="inlineStr">
@@ -14535,241 +14515,241 @@
     <row r="160" ht="108" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>w.of</t>
+          <t>set.info.intro</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Widget piccolo: sotto il numero. {obiettivo} = numero.</t>
+          <t>Riga che mostra di nuovo l'introduzione.</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>≤ 12</t>
+          <t>≤ 28</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>SU {obiettivo}</t>
+          <t>Rivedi l'introduzione</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>OF {obiettivo}</t>
+          <t>Replay introduction</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>DE {obiettivo}</t>
+          <t>Repetir la introducción</t>
         </is>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>SUR {obiettivo}</t>
+          <t>Revoir l’introduction</t>
         </is>
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>VON {obiettivo}</t>
+          <t>Einführung erneut ansehen</t>
         </is>
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>DE {obiettivo}</t>
+          <t>Rever a introdução</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr">
         <is>
-          <t>目標 {obiettivo}</t>
+          <t>はじめの説明をもう一度見る</t>
         </is>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
-          <t>목표 {obiettivo}</t>
+          <t>시작 안내 다시 보기</t>
         </is>
       </c>
       <c r="N160" s="6" t="inlineStr">
         <is>
-          <t>目标 {obiettivo}</t>
+          <t>重看介绍</t>
         </is>
       </c>
       <c r="O160" s="6" t="inlineStr">
         <is>
-          <t>目標 {obiettivo}</t>
+          <t>重看介紹</t>
         </is>
       </c>
       <c r="P160" s="6" t="inlineStr">
         <is>
-          <t>Conteggio letterale: EN 14/12, ES 14/12, FR 15/12, DE 15/12, PT-BR 14/12, JA 14/12, KO 14/12, ZH-Hans 14/12, ZH-Hant 14/12. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 9/12, ES 9/12, FR 10/12, DE 10/12, PT-BR 9/12, JA 9/12, KO 9/12, ZH-Hans 9/12, ZH-Hant 9/12. Verificare anche numeri più lunghi nella build.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>w.openApp</t>
+          <t>set.version</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Quando mancano i dati: invito ad aprire l'app, MAIUSCOLO.</t>
+          <t>Nota in fondo. {versione} = es. 1.0.</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>≤ 14</t>
+          <t>≤ 16</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>APRI L'APP</t>
+          <t>Versione {versione}</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>OPEN APP</t>
+          <t>Version {versione}</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>ABRIR APP</t>
+          <t>Versión {versione}</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>OUVRIR L’APP</t>
+          <t>Version {versione}</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>APP ÖFFNEN</t>
+          <t>Version {versione}</t>
         </is>
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>ABRIR APP</t>
+          <t>Versão {versione}</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr">
         <is>
-          <t>アプリを開く</t>
+          <t>バージョン {versione}</t>
         </is>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
-          <t>앱 열기</t>
+          <t>버전 {versione}</t>
         </is>
       </c>
       <c r="N161" s="6" t="inlineStr">
         <is>
-          <t>打开App</t>
+          <t>版本 {versione}</t>
         </is>
       </c>
       <c r="O161" s="6" t="inlineStr">
         <is>
-          <t>打開App</t>
+          <t>版本 {versione}</t>
         </is>
       </c>
       <c r="P161" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Conteggio letterale: EN 18/16, ES 18/16, FR 18/16, DE 18/16, PT-BR 17/16. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 11/16, ES 11/16, FR 11/16, DE 11/16, PT-BR 10/16. Verificare anche numeri più lunghi nella build.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>w.goal</t>
+          <t>party.title</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Widget medio a obiettivo chiuso, prima riga, MAIUSCOLO.</t>
+          <t>Schermata a tutto schermo quando chiudi l'obiettivo. Titolo gigante, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>≤ 10</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>OBIETTIVO</t>
+          <t>OBIETTIVO RAGGIUNTO!</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>GOAL REACHED!</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>OBJETIVO</t>
+          <t>¡OBJETIVO ALCANZADO!</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>OBJECTIF</t>
+          <t>OBJECTIF ATTEINT !</t>
         </is>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>ZIEL</t>
+          <t>ZIEL ERREICHT!</t>
         </is>
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>META ATINGIDA!</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>目標達成！</t>
         </is>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
-          <t>목표</t>
+          <t>목표 달성!</t>
         </is>
       </c>
       <c r="N162" s="6" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>目标达成！</t>
         </is>
       </c>
       <c r="O162" s="6" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>目標達成！</t>
         </is>
       </c>
       <c r="P162" s="6" t="inlineStr">
@@ -14781,323 +14761,323 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>w.done</t>
+          <t>party.of</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Seconda riga, MAIUSCOLO.</t>
+          <t>Sotto il numero dei passi. {obiettivo} = numero.</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>≤ 8</t>
+          <t>≤ 18</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>FATTO!</t>
+          <t>PASSI SU {obiettivo}</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>DONE!</t>
+          <t>OF {obiettivo} STEPS</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>¡LISTO!</t>
+          <t>PASOS DE {obiettivo}</t>
         </is>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>FAIT !</t>
+          <t>PAS SUR {obiettivo}</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>FERTIG!</t>
+          <t>VON {obiettivo} SCHR.</t>
         </is>
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>FEITO!</t>
+          <t>PASSOS DE {obiettivo}</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr">
         <is>
-          <t>やった！</t>
+          <t>目標 {obiettivo}歩</t>
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
-          <t>해냈다!</t>
+          <t>목표 {obiettivo}걸음</t>
         </is>
       </c>
       <c r="N163" s="6" t="inlineStr">
         <is>
-          <t>搞定！</t>
+          <t>目标 {obiettivo}步</t>
         </is>
       </c>
       <c r="O163" s="6" t="inlineStr">
         <is>
-          <t>搞定！</t>
+          <t>目標 {obiettivo}步</t>
         </is>
       </c>
       <c r="P163" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DE: SCHR. abbrevia l’unità per lo spazio; copre anche la flessione richiesta da VON. JA/KO/ZH: formato con obiettivo esplicito, più naturale nel blocco sotto il numero. Conteggio letterale: EN 20/18, ES 20/18, FR 19/18, DE 21/18, PT-BR 21/18. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 15/18, ES 15/18, FR 14/18, DE 16/18, PT-BR 16/18. Verificare anche numeri più lunghi nella build.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>w.left</t>
+          <t>party.streak.one</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Widget medio: etichetta sopra i minuti che mancano, MAIUSCOLO.</t>
+          <t>Riga sulla serie, singolare.</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>≤ 10</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>MANCANO</t>
+          <t>1 GIORNO DI FILA</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>LEFT</t>
+          <t>1 DAY IN A ROW</t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>FALTAN</t>
+          <t>1 DÍA SEGUIDO</t>
         </is>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>IL RESTE</t>
+          <t>1 J. D’AFFILÉE</t>
         </is>
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>ÜBRIG</t>
+          <t>1 TAG IN FOLGE</t>
         </is>
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>FALTAM</t>
+          <t>1 DIA SEGUIDO</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr">
         <is>
-          <t>あと</t>
+          <t>1日連続</t>
         </is>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>1일 연속</t>
         </is>
       </c>
       <c r="N164" s="6" t="inlineStr">
         <is>
-          <t>还需</t>
+          <t>连续1天</t>
         </is>
       </c>
       <c r="O164" s="6" t="inlineStr">
         <is>
-          <t>還需</t>
+          <t>連續1天</t>
         </is>
       </c>
       <c r="P164" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JA/KO/ZH: la forma non cambia per il plurale; conservato 1 in .one e {n} in .other, come negli originali. FR: J. abbrevia jour, in coerenza con il plurale e con il widget più stretto.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>w.minKm</t>
+          <t>party.streak.other</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Visibile</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Sotto il numero dei minuti. {km} = numero.</t>
+          <t>Plurale. {n} = numero.</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>≤ 16</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} GIORNI DI FILA</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} DAYS IN A ROW</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} DÍAS SEGUIDOS</t>
         </is>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} J. D’AFFILÉE</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} TAGE IN FOLGE</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>MIN · {km} KM</t>
+          <t>{n} DIAS SEGUIDOS</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr">
         <is>
-          <t>分・{km} KM</t>
+          <t>{n}日連続</t>
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
-          <t>분 · {km} KM</t>
+          <t>{n}일 연속</t>
         </is>
       </c>
       <c r="N165" s="6" t="inlineStr">
         <is>
-          <t>分钟 · {km} KM</t>
+          <t>连续{n}天</t>
         </is>
       </c>
       <c r="O165" s="6" t="inlineStr">
         <is>
-          <t>分鐘 · {km} KM</t>
+          <t>連續{n}天</t>
         </is>
       </c>
       <c r="P165" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FR: J. abbrevia jours, per lasciare spazio anche a serie di almeno 100 giorni nel widget. Stessa resa in w.lock.streak.other per coerenza con l’italiano identico. JA/KO/ZH: nessuna flessione di plurale.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>w.minMi</t>
+          <t>party.vo</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Come w.minKm, in miglia. {mi} = numero.</t>
+          <t>{passi}, {obiettivo} = numeri.</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>≤ 16</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Obiettivo raggiunto: {passi} passi su {obiettivo}</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Goal reached: {passi} steps of {obiettivo}</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Objetivo alcanzado: {passi} pasos de {obiettivo}</t>
         </is>
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Objectif atteint : {passi} pas sur {obiettivo}</t>
         </is>
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Ziel erreicht: {passi} Schritte von {obiettivo}</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>MIN · {mi} MI</t>
+          <t>Meta atingida: {passi} passos de {obiettivo}</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr">
         <is>
-          <t>分・{mi} MI</t>
+          <t>目標達成。{obiettivo}歩の目標に対し、{passi}歩です</t>
         </is>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
-          <t>분 · {mi} MI</t>
+          <t>목표 달성. 목표 {obiettivo}걸음 중 {passi}걸음을 걸었습니다</t>
         </is>
       </c>
       <c r="N166" s="6" t="inlineStr">
         <is>
-          <t>分钟 · {mi} MI</t>
+          <t>目标达成：已走{passi}步，目标{obiettivo}步</t>
         </is>
       </c>
       <c r="O166" s="6" t="inlineStr">
         <is>
-          <t>分鐘 · {mi} MI</t>
+          <t>目標達成：已走{passi}步，目標{obiettivo}步</t>
         </is>
       </c>
       <c r="P166" s="6" t="inlineStr">
@@ -15109,89 +15089,89 @@
     <row r="167" ht="36" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>w.lock.steps</t>
+          <t>party.close.vo</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Festa obiettivo</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Blocco schermo rettangolare: etichetta piccola, MAIUSCOLO.</t>
+          <t>Suggerimento: come chiuderla.</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>≤ 8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>PASSI</t>
+          <t>Tocca per chiudere</t>
         </is>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>STEPS</t>
+          <t>Tap to close</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>PASOS</t>
+          <t>Toca para cerrar</t>
         </is>
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>Touche pour fermer</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>SCHRITTE</t>
+          <t>Zum Schließen tippen</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>PASSOS</t>
+          <t>Toque para fechar</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr">
         <is>
-          <t>歩数</t>
+          <t>タップして閉じる</t>
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
-          <t>걸음 수</t>
+          <t>탭하여 닫기</t>
         </is>
       </c>
       <c r="N167" s="6" t="inlineStr">
         <is>
-          <t>步数</t>
+          <t>轻点以关闭</t>
         </is>
       </c>
       <c r="O167" s="6" t="inlineStr">
         <is>
-          <t>步數</t>
+          <t>點一下以關閉</t>
         </is>
       </c>
       <c r="P167" s="6" t="inlineStr">
         <is>
-          <t>DE: SCHRITTE per esteso nel limite 8; l’interruttore st.metric.steps usa la forma abbreviata SCHR. nel limite 6.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>w.lock.streak.one</t>
+          <t>w.gallery.name</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -15201,79 +15181,79 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Blocco schermo rettangolare: serie, singolare.</t>
+          <t>Nome del widget nella galleria dei widget di iOS.</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>≤ 18</t>
+          <t>≤ 24</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>1 GIORNO DI FILA</t>
+          <t>Passi di oggi</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>1 DAY IN A ROW</t>
+          <t>Today's steps</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>1 DÍA SEGUIDO</t>
+          <t>Pasos de hoy</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>1 J. D’AFFILÉE</t>
+          <t>Pas du jour</t>
         </is>
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>1 TAG IN FOLGE</t>
+          <t>Heutige Schritte</t>
         </is>
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>1 DIA SEGUIDO</t>
+          <t>Passos de hoje</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr">
         <is>
-          <t>1日連続</t>
+          <t>今日の歩数</t>
         </is>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
-          <t>1일 연속</t>
+          <t>오늘 걸음 수</t>
         </is>
       </c>
       <c r="N168" s="6" t="inlineStr">
         <is>
-          <t>连续1天</t>
+          <t>今日步数</t>
         </is>
       </c>
       <c r="O168" s="6" t="inlineStr">
         <is>
-          <t>連續1天</t>
+          <t>今日步數</t>
         </is>
       </c>
       <c r="P168" s="6" t="inlineStr">
         <is>
-          <t>FR: J. abbrevia jour; stessa traduzione di party.streak.one. JA/KO/ZH: medesima struttura della riga plurale, conservando 1 o {n}.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>w.lock.streak.other</t>
+          <t>w.gallery.desc</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -15283,79 +15263,79 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Plurale. {n} = numero.</t>
+          <t>Descrizione nella galleria dei widget.</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>≤ 18</t>
+          <t>≤ 70</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>{n} GIORNI DI FILA</t>
+          <t>Passi, minuti che mancano e serie, anche sul blocco schermo.</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>{n} DAYS IN A ROW</t>
+          <t>Steps, minutes left and your streak, even on the Lock Screen.</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>{n} DÍAS SEGUIDOS</t>
+          <t>Pasos, minutos restantes y racha, también en la pantalla de bloqueo.</t>
         </is>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t>{n} J. D’AFFILÉE</t>
+          <t>Pas, minutes restantes et série, même sur l’écran verrouillé.</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>{n} TAGE IN FOLGE</t>
+          <t>Schritte, übrige Minuten und Serie, auch auf dem Sperrbildschirm.</t>
         </is>
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>{n} DIAS SEGUIDOS</t>
+          <t>Passos, minutos restantes e sequência, até na Tela Bloqueada.</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
-          <t>{n}日連続</t>
+          <t>歩数、残り時間、連続記録をロック画面でもチェック。</t>
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>{n}일 연속</t>
+          <t>잠금 화면에서도 걸음 수, 남은 시간, 연속 기록을 확인해요.</t>
         </is>
       </c>
       <c r="N169" s="6" t="inlineStr">
         <is>
-          <t>连续{n}天</t>
+          <t>步数、剩余分钟数和连续记录，锁定屏幕上也能看。</t>
         </is>
       </c>
       <c r="O169" s="6" t="inlineStr">
         <is>
-          <t>連續{n}天</t>
+          <t>步數、剩餘分鐘數和連續紀錄，鎖定畫面上也能看。</t>
         </is>
       </c>
       <c r="P169" s="6" t="inlineStr">
         <is>
-          <t>FR: J. abbrevia jours per lasciare spazio ai numeri di tre o più cifre; stessa resa di party.streak.other. Controllare la leggibilità del widget nella build localizzata.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>w.lock.goalDone</t>
+          <t>w.stepsToday</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -15370,62 +15350,62 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Blocco schermo: obiettivo raggiunto, MAIUSCOLO.</t>
+          <t>Widget medio: etichetta sopra il numero dei passi, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>≤ 20</t>
+          <t>≤ 16</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>OBIETTIVO RAGGIUNTO</t>
+          <t>PASSI DI OGGI</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>GOAL REACHED</t>
+          <t>TODAY’S STEPS</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>OBJETIVO ALCANZADO</t>
+          <t>PASOS DE HOY</t>
         </is>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>OBJECTIF ATTEINT</t>
+          <t>PAS DU JOUR</t>
         </is>
       </c>
       <c r="J170" s="6" t="inlineStr">
         <is>
-          <t>ZIEL ERREICHT</t>
+          <t>HEUTIGE SCHRITTE</t>
         </is>
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>META ATINGIDA</t>
+          <t>PASSOS DE HOJE</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr">
         <is>
-          <t>目標達成</t>
+          <t>今日の歩数</t>
         </is>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
-          <t>목표 달성</t>
+          <t>오늘 걸음 수</t>
         </is>
       </c>
       <c r="N170" s="6" t="inlineStr">
         <is>
-          <t>目标达成</t>
+          <t>今日步数</t>
         </is>
       </c>
       <c r="O170" s="6" t="inlineStr">
         <is>
-          <t>目標達成</t>
+          <t>今日步數</t>
         </is>
       </c>
       <c r="P170" s="6" t="inlineStr">
@@ -15437,7 +15417,7 @@
     <row r="171" ht="60" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>w.lock.left</t>
+          <t>w.of</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
@@ -15452,74 +15432,74 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Blocco schermo: quanto manca. {min}, {km} = numeri.</t>
+          <t>Widget piccolo: sotto il numero. {obiettivo} = numero.</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>≤ 24</t>
+          <t>≤ 12</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>ANCORA {min} MIN · {km} KM</t>
+          <t>SU {obiettivo}</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
-          <t>{min} MIN LEFT · {km} KM</t>
+          <t>OF {obiettivo}</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>FALTAN {min} MIN · {km} KM</t>
+          <t>DE {obiettivo}</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>RESTE {min} MIN · {km} KM</t>
+          <t>SUR {obiettivo}</t>
         </is>
       </c>
       <c r="J171" s="6" t="inlineStr">
         <is>
-          <t>NOCH {min} MIN · {km} KM</t>
+          <t>VON {obiettivo}</t>
         </is>
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>FALTAM {min} MIN · {km} KM</t>
+          <t>DE {obiettivo}</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr">
         <is>
-          <t>あと{min}分・{km} KM</t>
+          <t>目標 {obiettivo}</t>
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>앞으로 {min}분 · {km} KM</t>
+          <t>목표 {obiettivo}</t>
         </is>
       </c>
       <c r="N171" s="6" t="inlineStr">
         <is>
-          <t>还需{min}分钟 · {km} KM</t>
+          <t>目标 {obiettivo}</t>
         </is>
       </c>
       <c r="O171" s="6" t="inlineStr">
         <is>
-          <t>還需{min}分鐘 · {km} KM</t>
+          <t>目標 {obiettivo}</t>
         </is>
       </c>
       <c r="P171" s="6" t="inlineStr">
         <is>
-          <t>Conteggio letterale: ES 26/24, FR 25/24, PT-BR 26/24. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: ES 23/24, FR 22/24, PT-BR 23/24. Verificare anche numeri più lunghi nella build.</t>
+          <t>Conteggio letterale: EN 14/12, ES 14/12, FR 15/12, DE 15/12, PT-BR 14/12, JA 14/12, KO 14/12, ZH-Hans 14/12, ZH-Hant 14/12. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: EN 9/12, ES 9/12, FR 10/12, DE 10/12, PT-BR 9/12, JA 9/12, KO 9/12, ZH-Hans 9/12, ZH-Hant 9/12. Verificare anche numeri più lunghi nella build.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="60" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>w.lock.left.mi</t>
+          <t>w.openApp</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -15534,62 +15514,62 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Come w.lock.left, in miglia. {min}, {mi} = numeri.</t>
+          <t>Quando mancano i dati: invito ad aprire l'app, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>≤ 24</t>
+          <t>≤ 14</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>ANCORA {min} MIN · {mi} MI</t>
+          <t>APRI L'APP</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>{min} MIN LEFT · {mi} MI</t>
+          <t>OPEN APP</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>FALTAN {min} MIN · {mi} MI</t>
+          <t>ABRIR APP</t>
         </is>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>RESTE {min} MIN · {mi} MI</t>
+          <t>OUVRIR L’APP</t>
         </is>
       </c>
       <c r="J172" s="6" t="inlineStr">
         <is>
-          <t>NOCH {min} MIN · {mi} MI</t>
+          <t>APP ÖFFNEN</t>
         </is>
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>FALTAM {min} MIN · {mi} MI</t>
+          <t>ABRIR APP</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr">
         <is>
-          <t>あと{min}分・{mi} MI</t>
+          <t>アプリを開く</t>
         </is>
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
-          <t>앞으로 {min}분 · {mi} MI</t>
+          <t>앱 열기</t>
         </is>
       </c>
       <c r="N172" s="6" t="inlineStr">
         <is>
-          <t>还需{min}分钟 · {mi} MI</t>
+          <t>打开App</t>
         </is>
       </c>
       <c r="O172" s="6" t="inlineStr">
         <is>
-          <t>還需{min}分鐘 · {mi} MI</t>
+          <t>打開App</t>
         </is>
       </c>
       <c r="P172" s="6" t="inlineStr">
@@ -15601,7 +15581,7 @@
     <row r="173" ht="36" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>w.inline</t>
+          <t>w.goal</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -15616,74 +15596,74 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Widget in linea sopra l'ora del blocco schermo. {passi} = numero.</t>
+          <t>Widget medio a obiettivo chiuso, prima riga, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>≤ 14</t>
+          <t>≤ 10</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>{passi} passi</t>
+          <t>OBIETTIVO</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>{passi} steps</t>
+          <t>GOAL</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>{passi} pasos</t>
+          <t>OBJETIVO</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>{passi} pas</t>
+          <t>OBJECTIF</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>{passi} Schr.</t>
+          <t>ZIEL</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>{passi} passos</t>
+          <t>META</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr">
         <is>
-          <t>{passi}歩</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
-          <t>{passi}걸음</t>
+          <t>목표</t>
         </is>
       </c>
       <c r="N173" s="6" t="inlineStr">
         <is>
-          <t>{passi}步</t>
+          <t>目标</t>
         </is>
       </c>
       <c r="O173" s="6" t="inlineStr">
         <is>
-          <t>{passi}步</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="P173" s="6" t="inlineStr">
         <is>
-          <t>DE: Schr. abbrevia Schritte nel widget in linea, per lasciare spazio al numero dei passi.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>w.inline.none</t>
+          <t>w.done</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -15698,62 +15678,62 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Widget in linea senza dati.</t>
+          <t>Seconda riga, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>≤ 10</t>
+          <t>≤ 8</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Passi —</t>
+          <t>FATTO!</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>Steps —</t>
+          <t>DONE!</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>Pasos —</t>
+          <t>¡LISTO!</t>
         </is>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>Pas —</t>
+          <t>FAIT !</t>
         </is>
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>Schritte —</t>
+          <t>FERTIG!</t>
         </is>
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>Passos —</t>
+          <t>FEITO!</t>
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr">
         <is>
-          <t>歩数 —</t>
+          <t>やった！</t>
         </is>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
-          <t>걸음 수 —</t>
+          <t>해냈다!</t>
         </is>
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
-          <t>步数 —</t>
+          <t>搞定！</t>
         </is>
       </c>
       <c r="O174" s="6" t="inlineStr">
         <is>
-          <t>步數 —</t>
+          <t>搞定！</t>
         </is>
       </c>
       <c r="P174" s="6" t="inlineStr">
@@ -15765,7 +15745,7 @@
     <row r="175" ht="60" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>w.thousands</t>
+          <t>w.left</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -15780,74 +15760,74 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Suffisso «migliaia» nel tondo del blocco schermo: 10.400 → 10,4K. Una lettera.</t>
+          <t>Widget medio: etichetta sopra i minuti che mancano, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>≤ 2</t>
+          <t>≤ 10</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>MANCANO</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>LEFT</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FALTAN</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>IL RESTE</t>
         </is>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>ÜBRIG</t>
         </is>
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FALTAM</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>あと</t>
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="N175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>还需</t>
         </is>
       </c>
       <c r="O175" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>還需</t>
         </is>
       </c>
       <c r="P175" s="6" t="inlineStr">
         <is>
-          <t>K mantiene il moltiplicatore 1000 in tutte le lingue. Non sostituito con 万/萬/만: richiederebbero un calcolo diverso. Verificare comprensibilità in JA/KO/ZH sul widget tondo.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>w.vo.none</t>
+          <t>w.minKm</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -15857,67 +15837,67 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Descrizione del widget senza dati.</t>
+          <t>Sotto il numero dei minuti. {km} = numero.</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 16</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Passi non disponibili: apri l'app</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Steps unavailable: open the app</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>Pasos no disponibles: abre la app</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>Pas indisponibles : ouvre l’app</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>Keine Schrittdaten verfügbar. Öffne die App</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>Passos indisponíveis: abra o app</t>
+          <t>MIN · {km} KM</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr">
         <is>
-          <t>歩数を取得できません。アプリを開いてください</t>
+          <t>分・{km} KM</t>
         </is>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
-          <t>걸음 수를 확인할 수 없습니다. 앱을 열어 주세요</t>
+          <t>분 · {km} KM</t>
         </is>
       </c>
       <c r="N176" s="6" t="inlineStr">
         <is>
-          <t>步数不可用，请打开App</t>
+          <t>分钟 · {km} KM</t>
         </is>
       </c>
       <c r="O176" s="6" t="inlineStr">
         <is>
-          <t>步數無法取得，請打開App</t>
+          <t>分鐘 · {km} KM</t>
         </is>
       </c>
       <c r="P176" s="6" t="inlineStr">
@@ -15929,7 +15909,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>w.vo.none.short</t>
+          <t>w.minMi</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -15939,67 +15919,67 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Descrizione breve senza dati.</t>
+          <t>Come w.minKm, in miglia. {mi} = numero.</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 16</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Passi non disponibili</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
-          <t>Steps unavailable</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>Pasos no disponibles</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
-          <t>Pas indisponibles</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="J177" s="6" t="inlineStr">
         <is>
-          <t>Keine Schrittdaten verfügbar</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>Passos indisponíveis</t>
+          <t>MIN · {mi} MI</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>歩数を取得できません</t>
+          <t>分・{mi} MI</t>
         </is>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>걸음 수를 확인할 수 없습니다</t>
+          <t>분 · {mi} MI</t>
         </is>
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
-          <t>步数不可用</t>
+          <t>分钟 · {mi} MI</t>
         </is>
       </c>
       <c r="O177" s="6" t="inlineStr">
         <is>
-          <t>步數無法取得</t>
+          <t>分鐘 · {mi} MI</t>
         </is>
       </c>
       <c r="P177" s="6" t="inlineStr">
@@ -16011,7 +15991,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>w.vo.steps</t>
+          <t>w.lock.steps</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -16021,79 +16001,79 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>{passi}, {obiettivo} = numeri.</t>
+          <t>Blocco schermo rettangolare: etichetta piccola, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 8</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>{passi} passi su {obiettivo}</t>
+          <t>PASSI</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>{passi} steps of {obiettivo}</t>
+          <t>STEPS</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>{passi} pasos de {obiettivo}</t>
+          <t>PASOS</t>
         </is>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>{passi} pas sur {obiettivo}</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="J178" s="6" t="inlineStr">
         <is>
-          <t>{passi} Schritte von {obiettivo}</t>
+          <t>SCHRITTE</t>
         </is>
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>{passi} passos de {obiettivo}</t>
+          <t>PASSOS</t>
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr">
         <is>
-          <t>目標{obiettivo}歩に対して{passi}歩</t>
+          <t>歩数</t>
         </is>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
-          <t>목표 {obiettivo}걸음 중 {passi}걸음</t>
+          <t>걸음 수</t>
         </is>
       </c>
       <c r="N178" s="6" t="inlineStr">
         <is>
-          <t>已走{passi}步，目标{obiettivo}步</t>
+          <t>步数</t>
         </is>
       </c>
       <c r="O178" s="6" t="inlineStr">
         <is>
-          <t>已走{passi}步，目標{obiettivo}步</t>
+          <t>步數</t>
         </is>
       </c>
       <c r="P178" s="6" t="inlineStr">
         <is>
-          <t>Frase iniziale a cui si aggiungono w.vo.done oppure w.vo.left, poi w.vo.streak. Controllare in VoiceOver la frase assemblata, non solo i frammenti isolati.</t>
+          <t>DE: SCHRITTE per esteso nel limite 8; l’interruttore st.metric.steps usa la forma abbreviata SCHR. nel limite 6.</t>
         </is>
       </c>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>w.vo.done</t>
+          <t>w.lock.streak.one</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -16103,79 +16083,79 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Si aggiunge alla frase sopra.</t>
+          <t>Blocco schermo rettangolare: serie, singolare.</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 18</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>, obiettivo raggiunto</t>
+          <t>1 GIORNO DI FILA</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>, goal reached</t>
+          <t>1 DAY IN A ROW</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>, objetivo alcanzado</t>
+          <t>1 DÍA SEGUIDO</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
-          <t>, objectif atteint</t>
+          <t>1 J. D’AFFILÉE</t>
         </is>
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>, Ziel erreicht</t>
+          <t>1 TAG IN FOLGE</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>, meta atingida</t>
+          <t>1 DIA SEGUIDO</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>、目標達成</t>
+          <t>1日連続</t>
         </is>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
-          <t>, 목표 달성</t>
+          <t>1일 연속</t>
         </is>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>，目标达成</t>
+          <t>连续1天</t>
         </is>
       </c>
       <c r="O179" s="6" t="inlineStr">
         <is>
-          <t>，目標達成</t>
+          <t>連續1天</t>
         </is>
       </c>
       <c r="P179" s="6" t="inlineStr">
         <is>
-          <t>Punteggiatura iniziale mantenuta o adattata alla lingua per unirsi a w.vo.steps.</t>
+          <t>FR: J. abbrevia jour; stessa traduzione di party.streak.one. JA/KO/ZH: medesima struttura della riga plurale, conservando 1 o {n}.</t>
         </is>
       </c>
     </row>
     <row r="180" ht="36" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>w.vo.left</t>
+          <t>w.lock.streak.other</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -16185,79 +16165,79 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Si aggiunge alla frase sopra. {min}, {km} = numeri.</t>
+          <t>Plurale. {n} = numero.</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 18</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>, mancano {min} minuti, {km} chilometri</t>
+          <t>{n} GIORNI DI FILA</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>, {min} minutes left, {km} kilometers</t>
+          <t>{n} DAYS IN A ROW</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>, faltan {min} minutos, {km} kilómetros</t>
+          <t>{n} DÍAS SEGUIDOS</t>
         </is>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>, il reste {min} minutes, {km} kilomètres</t>
+          <t>{n} J. D’AFFILÉE</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>, noch {min} Minuten, {km} Kilometer</t>
+          <t>{n} TAGE IN FOLGE</t>
         </is>
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>, faltam {min} minutos, {km} quilômetros</t>
+          <t>{n} DIAS SEGUIDOS</t>
         </is>
       </c>
       <c r="L180" s="6" t="inlineStr">
         <is>
-          <t>、あと{min}分、{km}キロメートル</t>
+          <t>{n}日連続</t>
         </is>
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
-          <t>, 남은 시간 {min}분, 거리 {km}킬로미터</t>
+          <t>{n}일 연속</t>
         </is>
       </c>
       <c r="N180" s="6" t="inlineStr">
         <is>
-          <t>，还需{min}分钟，{km}公里</t>
+          <t>连续{n}天</t>
         </is>
       </c>
       <c r="O180" s="6" t="inlineStr">
         <is>
-          <t>，還需{min}分鐘，{km}公里</t>
+          <t>連續{n}天</t>
         </is>
       </c>
       <c r="P180" s="6" t="inlineStr">
         <is>
-          <t>Punteggiatura iniziale mantenuta o adattata per unirsi a w.vo.steps. Le unità sono scritte per essere lette ad alta voce.</t>
+          <t>FR: J. abbrevia jours per lasciare spazio ai numeri di tre o più cifre; stessa resa di party.streak.other. Controllare la leggibilità del widget nella build localizzata.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="36" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>w.vo.left.mi</t>
+          <t>w.lock.goalDone</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -16267,67 +16247,67 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Come w.vo.left, in miglia: si aggiunge a w.vo.steps. {min}, {mi} = numeri.</t>
+          <t>Blocco schermo: obiettivo raggiunto, MAIUSCOLO.</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 20</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>, mancano {min} minuti, {mi} miglia</t>
+          <t>OBIETTIVO RAGGIUNTO</t>
         </is>
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>, {min} minutes left, {mi} miles</t>
+          <t>GOAL REACHED</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>, faltan {min} minutos, {mi} millas</t>
+          <t>OBJETIVO ALCANZADO</t>
         </is>
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
-          <t>, il reste {min} minutes, {mi} miles</t>
+          <t>OBJECTIF ATTEINT</t>
         </is>
       </c>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>, noch {min} Minuten, {mi} Meilen</t>
+          <t>ZIEL ERREICHT</t>
         </is>
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>, faltam {min} minutos, {mi} milhas</t>
+          <t>META ATINGIDA</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr">
         <is>
-          <t>、あと{min}分、{mi}マイル</t>
+          <t>目標達成</t>
         </is>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
-          <t>, 남은 시간 {min}분, 거리 {mi}마일</t>
+          <t>목표 달성</t>
         </is>
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
-          <t>，还需{min}分钟，{mi}英里</t>
+          <t>目标达成</t>
         </is>
       </c>
       <c r="O181" s="6" t="inlineStr">
         <is>
-          <t>，還需{min}分鐘，{mi}英里</t>
+          <t>目標達成</t>
         </is>
       </c>
       <c r="P181" s="6" t="inlineStr">
@@ -16339,7 +16319,7 @@
     <row r="182" ht="36" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>w.vo.streak</t>
+          <t>w.lock.left</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -16349,149 +16329,149 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Chiude la frase. {n} = giorni di serie, {jolly} = numero.</t>
+          <t>Blocco schermo: quanto manca. {min}, {km} = numeri.</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤ 24</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>. Serie: {n} giorni, Jolly: {jolly}</t>
+          <t>ANCORA {min} MIN · {km} KM</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>. Streak: {n} days, Jokers: {jolly}</t>
+          <t>{min} MIN LEFT · {km} KM</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>. Racha: {n} días, Comodines: {jolly}</t>
+          <t>FALTAN {min} MIN · {km} KM</t>
         </is>
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>. Série : {n} jours, Jokers : {jolly}</t>
+          <t>RESTE {min} MIN · {km} KM</t>
         </is>
       </c>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>. Serie: {n} Tage, Joker: {jolly}</t>
+          <t>NOCH {min} MIN · {km} KM</t>
         </is>
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>. Sequência: {n} dias, Coringas: {jolly}</t>
+          <t>FALTAM {min} MIN · {km} KM</t>
         </is>
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
-          <t>。連続記録：{n}日、おまもり：{jolly}個</t>
+          <t>あと{min}分・{km} KM</t>
         </is>
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
-          <t>. 연속 기록: {n}일, 지킴이: {jolly}개</t>
+          <t>앞으로 {min}분 · {km} KM</t>
         </is>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
-          <t>。连续记录：{n}天，护身符：{jolly}枚</t>
+          <t>还需{min}分钟 · {km} KM</t>
         </is>
       </c>
       <c r="O182" s="6" t="inlineStr">
         <is>
-          <t>。連續紀錄：{n}天，護身符：{jolly}枚</t>
+          <t>還需{min}分鐘 · {km} KM</t>
         </is>
       </c>
       <c r="P182" s="6" t="inlineStr">
         <is>
-          <t>Frammento finale della descrizione completa. JA/KO/ZH: verificare fluidità, pronuncia dei contatori e dei nomi dei bonus.</t>
+          <t>Conteggio letterale: ES 26/24, FR 25/24, PT-BR 26/24. Include i nomi dei segnaposto, copiati identici. Con valori di esempio: ES 23/24, FR 22/24, PT-BR 23/24. Verificare anche numeri più lunghi nella build.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>n.title</t>
+          <t>w.lock.left.mi</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Titolo della notifica del promemoria (giorno di oggi).</t>
+          <t>Come w.lock.left, in miglia. {min}, {mi} = numeri.</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>≤ 30</t>
+          <t>≤ 24</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Minuti sul tappeto</t>
+          <t>ANCORA {min} MIN · {mi} MI</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>Minutes on the treadmill</t>
+          <t>{min} MIN LEFT · {mi} MI</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>Minutos en la cinta de correr</t>
+          <t>FALTAN {min} MIN · {mi} MI</t>
         </is>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
-          <t>Minutes sur tapis de course</t>
+          <t>RESTE {min} MIN · {mi} MI</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Minuten auf dem Laufband</t>
+          <t>NOCH {min} MIN · {mi} MI</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>Minutos na esteira</t>
+          <t>FALTAM {min} MIN · {mi} MI</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
-          <t>トレッドミルの時間</t>
+          <t>あと{min}分・{mi} MI</t>
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
-          <t>러닝머신에서 필요한 시간</t>
+          <t>앞으로 {min}분 · {mi} MI</t>
         </is>
       </c>
       <c r="N183" s="6" t="inlineStr">
         <is>
-          <t>跑步机所需分钟数</t>
+          <t>还需{min}分钟 · {mi} MI</t>
         </is>
       </c>
       <c r="O183" s="6" t="inlineStr">
         <is>
-          <t>跑步機所需分鐘數</t>
+          <t>還需{min}分鐘 · {mi} MI</t>
         </is>
       </c>
       <c r="P183" s="6" t="inlineStr">
@@ -16503,159 +16483,159 @@
     <row r="184" ht="36" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>n.body</t>
+          <t>w.inline</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Corpo. {min} = minuti, {velocita} = km/h, {obiettivo} = passi obiettivo, {mancano} = passi mancanti.</t>
+          <t>Widget in linea sopra l'ora del blocco schermo. {passi} = numero.</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>≤ 140</t>
+          <t>≤ 14</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Ti servono {min} min a {velocita} km/h per chiudere i {obiettivo} passi (mancano {mancano}).</t>
+          <t>{passi} passi</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>You need {min} min at {velocita} km/h to reach {obiettivo} steps ({mancano} left).</t>
+          <t>{passi} steps</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>Necesitas {min} min a {velocita} km/h para alcanzar {obiettivo} pasos (faltan {mancano}).</t>
+          <t>{passi} pasos</t>
         </is>
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
-          <t>Il te faut {min} min à {velocita} km/h pour atteindre {obiettivo} pas (il en manque {mancano}).</t>
+          <t>{passi} pas</t>
         </is>
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>Du brauchst {min} min bei {velocita} km/h für {obiettivo} Schritte (noch {mancano}).</t>
+          <t>{passi} Schr.</t>
         </is>
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>Você precisa de {min} min a {velocita} km/h para atingir {obiettivo} passos (faltam {mancano}).</t>
+          <t>{passi} passos</t>
         </is>
       </c>
       <c r="L184" s="6" t="inlineStr">
         <is>
-          <t>目標の{obiettivo}歩まで、あと{mancano}歩。{velocita} km/hで{min}分必要だよ。</t>
+          <t>{passi}歩</t>
         </is>
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
-          <t>목표 {obiettivo}걸음까지 {mancano}걸음 남았어요. {velocita} km/h로 {min}분이 필요해요.</t>
+          <t>{passi}걸음</t>
         </is>
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
-          <t>还差{mancano}步即可达到{obiettivo}步。以{velocita} km/h的速度，需要{min}分钟。</t>
+          <t>{passi}步</t>
         </is>
       </c>
       <c r="O184" s="6" t="inlineStr">
         <is>
-          <t>還差{mancano}步即可達到{obiettivo}步。以{velocita} km/h的速度，需要{min}分鐘。</t>
+          <t>{passi}步</t>
         </is>
       </c>
       <c r="P184" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DE: Schr. abbrevia Schritte nel widget in linea, per lasciare spazio al numero dei passi.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>n.body.mi</t>
+          <t>w.inline.none</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Come n.body, con la velocità in mph. {min} = minuti, {velocita} = mph, {obiettivo} = passi obiettivo, {mancano} = passi mancanti.</t>
+          <t>Widget in linea senza dati.</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>≤ 140</t>
+          <t>≤ 10</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Ti servono {min} min a {velocita} mph per chiudere i {obiettivo} passi (mancano {mancano}).</t>
+          <t>Passi —</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>You need {min} min at {velocita} mph to reach {obiettivo} steps ({mancano} left).</t>
+          <t>Steps —</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>Necesitas {min} min a {velocita} mph para alcanzar {obiettivo} pasos (faltan {mancano}).</t>
+          <t>Pasos —</t>
         </is>
       </c>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t>Il te faut {min} min à {velocita} mph pour atteindre {obiettivo} pas (il en manque {mancano}).</t>
+          <t>Pas —</t>
         </is>
       </c>
       <c r="J185" s="6" t="inlineStr">
         <is>
-          <t>Du brauchst {min} min bei {velocita} mph für {obiettivo} Schritte (noch {mancano}).</t>
+          <t>Schritte —</t>
         </is>
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>Você precisa de {min} min a {velocita} mph para atingir {obiettivo} passos (faltam {mancano}).</t>
+          <t>Passos —</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr">
         <is>
-          <t>目標の{obiettivo}歩まで、あと{mancano}歩。{velocita} mphで{min}分必要だよ。</t>
+          <t>歩数 —</t>
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
-          <t>목표 {obiettivo}걸음까지 {mancano}걸음 남았어요. {velocita} mph로 {min}분이 필요해요.</t>
+          <t>걸음 수 —</t>
         </is>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>还差{mancano}步即可达到{obiettivo}步。以{velocita} mph的速度，需要{min}分钟。</t>
+          <t>步数 —</t>
         </is>
       </c>
       <c r="O185" s="6" t="inlineStr">
         <is>
-          <t>還差{mancano}步即可達到{obiettivo}步。以{velocita} mph的速度，需要{min}分鐘。</t>
+          <t>步數 —</t>
         </is>
       </c>
       <c r="P185" s="6" t="inlineStr">
@@ -16667,159 +16647,159 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>n.jolly</t>
+          <t>w.thousands</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Frase aggiunta se domani si userebbe un Jolly. {n} = Jolly che resterebbero.</t>
+          <t>Suffisso «migliaia» nel tondo del blocco schermo: 10.400 → 10,4K. Una lettera.</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>≤ 80</t>
+          <t>≤ 2</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Se non chiudi, stasera usi un Jolly (ne restano {n}).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>Miss your goal tonight and a Joker will be used ({n} left).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>Si no alcanzas tu objetivo, esta noche se usará un Comodín (quedarán {n}).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
-          <t>Sans atteindre ton objectif, un Joker sera utilisé ce soir (il en restera {n}).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="J186" s="6" t="inlineStr">
         <is>
-          <t>Erreichst du dein Ziel nicht, wird heute ein Joker genutzt ({n} übrig).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>Se não atingir sua meta, um Coringa será usado esta noite (restarão {n}).</t>
+          <t>K</t>
         </is>
       </c>
       <c r="L186" s="6" t="inlineStr">
         <is>
-          <t>目標未達成なら今夜おまもりを1個使うよ（残り{n}個）。</t>
+          <t>K</t>
         </is>
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
-          <t>목표를 달성하지 못하면 오늘 밤 지킴이 1개가 사용돼요. {n}개가 남아요.</t>
+          <t>K</t>
         </is>
       </c>
       <c r="N186" s="6" t="inlineStr">
         <is>
-          <t>若未达成目标，今晚将使用1枚护身符（剩余{n}枚）。</t>
+          <t>K</t>
         </is>
       </c>
       <c r="O186" s="6" t="inlineStr">
         <is>
-          <t>若未達成目標，今晚將使用1枚護身符（剩餘{n}枚）。</t>
+          <t>K</t>
         </is>
       </c>
       <c r="P186" s="6" t="inlineStr">
         <is>
-          <t>Resa esplicita l’attivazione automatica già descritta nelle regole. {n} indica i Jolly che restano dopo il consumo, non quelli disponibili prima.</t>
+          <t>K mantiene il moltiplicatore 1000 in tutte le lingue. Non sostituito con 万/萬/만: richiederebbero un calcolo diverso. Verificare comprensibilità in JA/KO/ZH sul widget tondo.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>n.lose</t>
+          <t>w.vo.none</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Frase aggiunta se non ci sono Jolly. {n} = giorni di serie.</t>
+          <t>Descrizione del widget senza dati.</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>≤ 80</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Senza Jolly, la streak di {n} giorni si interrompe.</t>
+          <t>Passi non disponibili: apri l'app</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>Without a Joker, your {n}-day streak ends.</t>
+          <t>Steps unavailable: open the app</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>Sin Comodines, tu racha de {n} días se interrumpe.</t>
+          <t>Pasos no disponibles: abre la app</t>
         </is>
       </c>
       <c r="I187" s="6" t="inlineStr">
         <is>
-          <t>Sans Joker, ta série de {n} jours s’arrête.</t>
+          <t>Pas indisponibles : ouvre l’app</t>
         </is>
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Ohne Joker endet deine Serie von {n} Tagen.</t>
+          <t>Keine Schrittdaten verfügbar. Öffne die App</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>Sem Coringas, sua sequência de {n} dias será interrompida.</t>
+          <t>Passos indisponíveis: abra o app</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>おまもりがないため、{n}日間の連続記録が途切れるよ。</t>
+          <t>歩数を取得できません。アプリを開いてください</t>
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
-          <t>지킴이가 없으면 {n}일의 연속 기록이 끊겨요.</t>
+          <t>걸음 수를 확인할 수 없습니다. 앱을 열어 주세요</t>
         </is>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>没有护身符，{n}天的连续记录将中断。</t>
+          <t>步数不可用，请打开App</t>
         </is>
       </c>
       <c r="O187" s="6" t="inlineStr">
         <is>
-          <t>沒有護身符，{n}天的連續紀錄將中斷。</t>
+          <t>步數無法取得，請打開App</t>
         </is>
       </c>
       <c r="P187" s="6" t="inlineStr">
@@ -16831,77 +16811,77 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>n.generic.title</t>
+          <t>w.vo.none.short</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Titolo per i giorni futuri (passi non ancora noti).</t>
+          <t>Descrizione breve senza dati.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>≤ 30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>È ora del tappeto?</t>
+          <t>Passi non disponibili</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Time for the treadmill?</t>
+          <t>Steps unavailable</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>¿Hora de la cinta de correr?</t>
+          <t>Pasos no disponibles</t>
         </is>
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>L’heure du tapis de course ?</t>
+          <t>Pas indisponibles</t>
         </is>
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>Zeit fürs Laufband?</t>
+          <t>Keine Schrittdaten verfügbar</t>
         </is>
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>Hora da esteira?</t>
+          <t>Passos indisponíveis</t>
         </is>
       </c>
       <c r="L188" s="6" t="inlineStr">
         <is>
-          <t>トレッドミルの時間？</t>
+          <t>歩数を取得できません</t>
         </is>
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
-          <t>러닝머신 탈 시간인가요?</t>
+          <t>걸음 수를 확인할 수 없습니다</t>
         </is>
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
-          <t>该上跑步机了吗？</t>
+          <t>步数不可用</t>
         </is>
       </c>
       <c r="O188" s="6" t="inlineStr">
         <is>
-          <t>該上跑步機了嗎？</t>
+          <t>步數無法取得</t>
         </is>
       </c>
       <c r="P188" s="6" t="inlineStr">
@@ -16913,326 +16893,1228 @@
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>n.generic.body</t>
+          <t>w.vo.steps</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Notifica serale</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Notifica</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Corpo per i giorni futuri.</t>
+          <t>{passi}, {obiettivo} = numeri.</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>≤ 80</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Apri NEAT per vedere quanti minuti ti servono stasera.</t>
+          <t>{passi} passi su {obiettivo}</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>Open NEAT to see how many minutes you need tonight.</t>
+          <t>{passi} steps of {obiettivo}</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>Abre NEAT para ver cuántos minutos necesitas esta noche.</t>
+          <t>{passi} pasos de {obiettivo}</t>
         </is>
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
-          <t>Ouvre NEAT pour voir combien de minutes il te faut ce soir.</t>
+          <t>{passi} pas sur {obiettivo}</t>
         </is>
       </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>Öffne NEAT und sieh, wie viele Minuten du heute Abend brauchst.</t>
+          <t>{passi} Schritte von {obiettivo}</t>
         </is>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>Abra o NEAT para ver quantos minutos você precisa esta noite.</t>
+          <t>{passi} passos de {obiettivo}</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr">
         <is>
-          <t>NEATを開いて、今夜あと何分必要か見てみよう。</t>
+          <t>目標{obiettivo}歩に対して{passi}歩</t>
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
-          <t>NEAT를 열어 오늘 저녁 몇 분이 필요한지 확인해 보세요.</t>
+          <t>목표 {obiettivo}걸음 중 {passi}걸음</t>
         </is>
       </c>
       <c r="N189" s="6" t="inlineStr">
         <is>
-          <t>打开NEAT，看看今晚还需要多少分钟。</t>
+          <t>已走{passi}步，目标{obiettivo}步</t>
         </is>
       </c>
       <c r="O189" s="6" t="inlineStr">
         <is>
-          <t>打開NEAT，看看今晚還需要幾分鐘。</t>
+          <t>已走{passi}步，目標{obiettivo}步</t>
         </is>
       </c>
       <c r="P189" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Frase iniziale a cui si aggiungono w.vo.done oppure w.vo.left, poi w.vo.streak. Controllare in VoiceOver la frase assemblata, non solo i frammenti isolati.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="84" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>p.health.read</t>
+          <t>w.vo.done</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Permessi (finestre di iOS)</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Testo che iOS mostra quando l'app chiede di leggere da Salute. Tono formale-chiaro, è anche controllato da Apple.</t>
+          <t>Si aggiunge alla frase sopra.</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>≤ 250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>NEAT legge i tuoi passi di oggi per calcolare quanti minuti di tappeto ti servono, e i tuoi allenamenti di camminata e corsa (passi, distanza, durata) per tarare la cadenza. Non scrive nulla e non invia dati fuori dal telefono.</t>
+          <t>, obiettivo raggiunto</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>NEAT reads today's steps to calculate the treadmill minutes you need, and your walking and running workouts (steps, distance, duration) to calibrate your cadence. It writes nothing and sends no data off your phone.</t>
+          <t>, goal reached</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>NEAT lee tus pasos de hoy para calcular los minutos de cinta de correr que necesitas, y tus entrenamientos de caminata y carrera (pasos, distancia, duración) para calibrar tu cadencia. No escribe nada ni envía datos fuera del teléfono.</t>
+          <t>, objetivo alcanzado</t>
         </is>
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>NEAT lit tes pas du jour pour calculer les minutes nécessaires sur tapis de course et tes entraînements de marche et de course (pas, distance, durée) pour calibrer ta cadence. Aucune écriture ni envoi de données hors du téléphone.</t>
+          <t>, objectif atteint</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>NEAT liest heutige Schritte für die nötigen Laufbandminuten und deine Geh- und Lauftrainings (Schritte, Strecke, Dauer) zur Kalibrierung deiner Schrittfrequenz. Schreibt nichts und sendet keine Daten vom Handy.</t>
+          <t>, Ziel erreicht</t>
         </is>
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>O NEAT lê seus passos de hoje para calcular os minutos de esteira necessários e seus exercícios de caminhada e corrida (passos, distância, duração) para calibrar sua cadência. Não grava nada nem envia dados para fora do celular.</t>
+          <t>, meta atingida</t>
         </is>
       </c>
       <c r="L190" s="6" t="inlineStr">
         <is>
-          <t>NEATは今日の歩数を読み取り、トレッドミルで必要な時間を計算します。また、ウォーキングとランニングのワークアウト（歩数、距離、時間）を読み取り、計算に使う1分あたりの歩数を調整します。データの書き込みやスマホ外への送信は行いません。</t>
+          <t>、目標達成</t>
         </is>
       </c>
       <c r="M190" s="6" t="inlineStr">
         <is>
-          <t>NEAT는 오늘 걸음 수를 읽어 러닝머신에서 필요한 시간을 계산하고, 걷기와 달리기 운동 기록(걸음 수, 거리, 시간)을 읽어 계산에 쓰는 분당 걸음 수를 보정합니다. 데이터를 쓰거나 휴대폰 밖으로 보내지 않습니다.</t>
+          <t>, 목표 달성</t>
         </is>
       </c>
       <c r="N190" s="6" t="inlineStr">
         <is>
-          <t>NEAT读取今日步数，计算所需的跑步机运动分钟数，并读取你的步行和跑步体能训练（步数、距离、时长）以校准步频。不写入任何内容，也不向手机外发送数据。</t>
+          <t>，目标达成</t>
         </is>
       </c>
       <c r="O190" s="6" t="inlineStr">
         <is>
-          <t>NEAT讀取今日步數，計算所需的跑步機運動分鐘數，並讀取你的步行和跑步體能訓練（步數、距離、時間長度）以校正步頻。不寫入任何內容，也不向手機外傳送資料。</t>
+          <t>，目標達成</t>
         </is>
       </c>
       <c r="P190" s="6" t="inlineStr">
         <is>
-          <t>Permesso: mantenuti passi di oggi, minuti sul tapis roulant, allenamenti di camminata/corsa, passi/distanza/durata per tarare la cadenza, nessuna scrittura o invio dal telefono. JA/KO spiegano la cadenza come passi al minuto. Revisione madrelingua consigliata per JA/KO/ZH.</t>
+          <t>Punteggiatura iniziale mantenuta o adattata alla lingua per unirsi a w.vo.steps.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="60" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>p.health.write</t>
+          <t>w.vo.left</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Permessi (finestre di iOS)</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>VoiceOver</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Testo obbligatorio per Apple anche se l'app non scrive.</t>
+          <t>Si aggiunge alla frase sopra. {min}, {km} = numeri.</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>≤ 200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>NEAT non scrive nulla in Salute: si limita a leggere i dati. Questa dichiarazione è richiesta da Apple per le app con accesso a Salute.</t>
+          <t>, mancano {min} minuti, {km} chilometri</t>
         </is>
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>NEAT writes nothing to Health: it only reads data. Apple requires this statement for apps with Health access.</t>
+          <t>, {min} minutes left, {km} kilometers</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>NEAT no escribe nada en Salud: solo lee datos. Apple exige esta declaración para las apps con acceso a Salud.</t>
+          <t>, faltan {min} minutos, {km} kilómetros</t>
         </is>
       </c>
       <c r="I191" s="6" t="inlineStr">
         <is>
-          <t>NEAT n’écrit rien dans Santé : l’app se contente de lire les données. Apple exige cette déclaration pour les apps ayant accès à Santé.</t>
+          <t>, il reste {min} minutes, {km} kilomètres</t>
         </is>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>NEAT schreibt nichts in Health, sondern liest nur Daten. Apple verlangt diese Erklärung für Apps mit Health-Zugriff.</t>
+          <t>, noch {min} Minuten, {km} Kilometer</t>
         </is>
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>O NEAT não grava nada no Saúde: apenas lê dados. A Apple exige esta declaração para apps com acesso ao Saúde.</t>
+          <t>, faltam {min} minutos, {km} quilômetros</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr">
         <is>
-          <t>NEATはヘルスケアへの書き込みは行わず、データの読み取りのみを行います。この説明は、ヘルスケアにアクセスするアプリにAppleが義務付けているものです。</t>
+          <t>、あと{min}分、{km}キロメートル</t>
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
-          <t>NEAT는 건강 앱에 아무것도 쓰지 않고 데이터를 읽기만 합니다. Apple은 건강 앱에 접근하는 앱에 이 설명을 요구합니다.</t>
+          <t>, 남은 시간 {min}분, 거리 {km}킬로미터</t>
         </is>
       </c>
       <c r="N191" s="6" t="inlineStr">
         <is>
-          <t>NEAT不向“健康”写入任何内容，只读取数据。Apple要求访问“健康”的App提供此声明。</t>
+          <t>，还需{min}分钟，{km}公里</t>
         </is>
       </c>
       <c r="O191" s="6" t="inlineStr">
         <is>
-          <t>NEAT不向「健康」寫入任何內容，只讀取資料。Apple要求存取「健康」的App提供此聲明。</t>
+          <t>，還需{min}分鐘，{km}公里</t>
         </is>
       </c>
       <c r="P191" s="6" t="inlineStr">
         <is>
-          <t>Traduzione fedele: l’originale dice soltanto i passi, mentre p.health.read include anche gli allenamenti. Verificare la coerenza dell’italiano prima della pubblicazione; non corretto unilateralmente il testo di partenza. | COORDINAMENTO: italiano corretto («legge soltanto i tuoi passi» era inesatto: legge anche allenamenti e distanza) e traduzioni allineate. Da riportare nell'Info.plist.</t>
+          <t>Punteggiatura iniziale mantenuta o adattata per unirsi a w.vo.steps. Le unità sono scritte per essere lette ad alta voce.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
         <is>
+          <t>w.vo.left.mi</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>VoiceOver</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>Come w.vo.left, in miglia: si aggiunge a w.vo.steps. {min}, {mi} = numeri.</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>, mancano {min} minuti, {mi} miglia</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>, {min} minutes left, {mi} miles</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>, faltan {min} minutos, {mi} millas</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>, il reste {min} minutes, {mi} miles</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>, noch {min} Minuten, {mi} Meilen</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>, faltam {min} minutos, {mi} milhas</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr">
+        <is>
+          <t>、あと{min}分、{mi}マイル</t>
+        </is>
+      </c>
+      <c r="M192" s="6" t="inlineStr">
+        <is>
+          <t>, 남은 시간 {min}분, 거리 {mi}마일</t>
+        </is>
+      </c>
+      <c r="N192" s="6" t="inlineStr">
+        <is>
+          <t>，还需{min}分钟，{mi}英里</t>
+        </is>
+      </c>
+      <c r="O192" s="6" t="inlineStr">
+        <is>
+          <t>，還需{min}分鐘，{mi}英里</t>
+        </is>
+      </c>
+      <c r="P192" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>w.vo.streak</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>VoiceOver</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>Chiude la frase. {n} = giorni di serie, {jolly} = numero.</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>. Serie: {n} giorni, Jolly: {jolly}</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>. Streak: {n} days, Jokers: {jolly}</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>. Racha: {n} días, Comodines: {jolly}</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>. Série : {n} jours, Jokers : {jolly}</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>. Serie: {n} Tage, Joker: {jolly}</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>. Sequência: {n} dias, Coringas: {jolly}</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>。連続記録：{n}日、おまもり：{jolly}個</t>
+        </is>
+      </c>
+      <c r="M193" s="6" t="inlineStr">
+        <is>
+          <t>. 연속 기록: {n}일, 지킴이: {jolly}개</t>
+        </is>
+      </c>
+      <c r="N193" s="6" t="inlineStr">
+        <is>
+          <t>。连续记录：{n}天，护身符：{jolly}枚</t>
+        </is>
+      </c>
+      <c r="O193" s="6" t="inlineStr">
+        <is>
+          <t>。連續紀錄：{n}天，護身符：{jolly}枚</t>
+        </is>
+      </c>
+      <c r="P193" s="6" t="inlineStr">
+        <is>
+          <t>Frammento finale della descrizione completa. JA/KO/ZH: verificare fluidità, pronuncia dei contatori e dei nomi dei bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>n.title</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Titolo della notifica del promemoria (giorno di oggi).</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>≤ 30</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Minuti sul tappeto</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Minutes on the treadmill</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>Minutos en la cinta de correr</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>Minutes sur tapis de course</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t>Minuten auf dem Laufband</t>
+        </is>
+      </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>Minutos na esteira</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr">
+        <is>
+          <t>トレッドミルの時間</t>
+        </is>
+      </c>
+      <c r="M194" s="6" t="inlineStr">
+        <is>
+          <t>러닝머신에서 필요한 시간</t>
+        </is>
+      </c>
+      <c r="N194" s="6" t="inlineStr">
+        <is>
+          <t>跑步机所需分钟数</t>
+        </is>
+      </c>
+      <c r="O194" s="6" t="inlineStr">
+        <is>
+          <t>跑步機所需分鐘數</t>
+        </is>
+      </c>
+      <c r="P194" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>n.body</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Corpo. {min} = minuti, {velocita} = km/h, {obiettivo} = passi obiettivo, {mancano} = passi mancanti.</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>≤ 140</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>Ti servono {min} min a {velocita} km/h per chiudere i {obiettivo} passi (mancano {mancano}).</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>You need {min} min at {velocita} km/h to reach {obiettivo} steps ({mancano} left).</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>Necesitas {min} min a {velocita} km/h para alcanzar {obiettivo} pasos (faltan {mancano}).</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>Il te faut {min} min à {velocita} km/h pour atteindre {obiettivo} pas (il en manque {mancano}).</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>Du brauchst {min} min bei {velocita} km/h für {obiettivo} Schritte (noch {mancano}).</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>Você precisa de {min} min a {velocita} km/h para atingir {obiettivo} passos (faltam {mancano}).</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr">
+        <is>
+          <t>目標の{obiettivo}歩まで、あと{mancano}歩。{velocita} km/hで{min}分必要だよ。</t>
+        </is>
+      </c>
+      <c r="M195" s="6" t="inlineStr">
+        <is>
+          <t>목표 {obiettivo}걸음까지 {mancano}걸음 남았어요. {velocita} km/h로 {min}분이 필요해요.</t>
+        </is>
+      </c>
+      <c r="N195" s="6" t="inlineStr">
+        <is>
+          <t>还差{mancano}步即可达到{obiettivo}步。以{velocita} km/h的速度，需要{min}分钟。</t>
+        </is>
+      </c>
+      <c r="O195" s="6" t="inlineStr">
+        <is>
+          <t>還差{mancano}步即可達到{obiettivo}步。以{velocita} km/h的速度，需要{min}分鐘。</t>
+        </is>
+      </c>
+      <c r="P195" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>n.body.mi</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>Come n.body, con la velocità in mph. {min} = minuti, {velocita} = mph, {obiettivo} = passi obiettivo, {mancano} = passi mancanti.</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>≤ 140</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>Ti servono {min} min a {velocita} mph per chiudere i {obiettivo} passi (mancano {mancano}).</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>You need {min} min at {velocita} mph to reach {obiettivo} steps ({mancano} left).</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>Necesitas {min} min a {velocita} mph para alcanzar {obiettivo} pasos (faltan {mancano}).</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>Il te faut {min} min à {velocita} mph pour atteindre {obiettivo} pas (il en manque {mancano}).</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>Du brauchst {min} min bei {velocita} mph für {obiettivo} Schritte (noch {mancano}).</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>Você precisa de {min} min a {velocita} mph para atingir {obiettivo} passos (faltam {mancano}).</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>目標の{obiettivo}歩まで、あと{mancano}歩。{velocita} mphで{min}分必要だよ。</t>
+        </is>
+      </c>
+      <c r="M196" s="6" t="inlineStr">
+        <is>
+          <t>목표 {obiettivo}걸음까지 {mancano}걸음 남았어요. {velocita} mph로 {min}분이 필요해요.</t>
+        </is>
+      </c>
+      <c r="N196" s="6" t="inlineStr">
+        <is>
+          <t>还差{mancano}步即可达到{obiettivo}步。以{velocita} mph的速度，需要{min}分钟。</t>
+        </is>
+      </c>
+      <c r="O196" s="6" t="inlineStr">
+        <is>
+          <t>還差{mancano}步即可達到{obiettivo}步。以{velocita} mph的速度，需要{min}分鐘。</t>
+        </is>
+      </c>
+      <c r="P196" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>n.jolly</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Frase aggiunta se domani si userebbe un Jolly. {n} = Jolly che resterebbero.</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>≤ 80</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Se non chiudi, stasera usi un Jolly (ne restano {n}).</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>Miss your goal tonight and a Joker will be used ({n} left).</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>Si no alcanzas tu objetivo, esta noche se usará un Comodín (quedarán {n}).</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>Sans atteindre ton objectif, un Joker sera utilisé ce soir (il en restera {n}).</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>Erreichst du dein Ziel nicht, wird heute ein Joker genutzt ({n} übrig).</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>Se não atingir sua meta, um Coringa será usado esta noite (restarão {n}).</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>目標未達成なら今夜おまもりを1個使うよ（残り{n}個）。</t>
+        </is>
+      </c>
+      <c r="M197" s="6" t="inlineStr">
+        <is>
+          <t>목표를 달성하지 못하면 오늘 밤 지킴이 1개가 사용돼요. {n}개가 남아요.</t>
+        </is>
+      </c>
+      <c r="N197" s="6" t="inlineStr">
+        <is>
+          <t>若未达成目标，今晚将使用1枚护身符（剩余{n}枚）。</t>
+        </is>
+      </c>
+      <c r="O197" s="6" t="inlineStr">
+        <is>
+          <t>若未達成目標，今晚將使用1枚護身符（剩餘{n}枚）。</t>
+        </is>
+      </c>
+      <c r="P197" s="6" t="inlineStr">
+        <is>
+          <t>Resa esplicita l’attivazione automatica già descritta nelle regole. {n} indica i Jolly che restano dopo il consumo, non quelli disponibili prima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>n.lose</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>Frase aggiunta se non ci sono Jolly. {n} = giorni di serie.</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>≤ 80</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Senza Jolly, la streak di {n} giorni si interrompe.</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Without a Joker, your {n}-day streak ends.</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>Sin Comodines, tu racha de {n} días se interrumpe.</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>Sans Joker, ta série de {n} jours s’arrête.</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>Ohne Joker endet deine Serie von {n} Tagen.</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>Sem Coringas, sua sequência de {n} dias será interrompida.</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr">
+        <is>
+          <t>おまもりがないため、{n}日間の連続記録が途切れるよ。</t>
+        </is>
+      </c>
+      <c r="M198" s="6" t="inlineStr">
+        <is>
+          <t>지킴이가 없으면 {n}일의 연속 기록이 끊겨요.</t>
+        </is>
+      </c>
+      <c r="N198" s="6" t="inlineStr">
+        <is>
+          <t>没有护身符，{n}天的连续记录将中断。</t>
+        </is>
+      </c>
+      <c r="O198" s="6" t="inlineStr">
+        <is>
+          <t>沒有護身符，{n}天的連續紀錄將中斷。</t>
+        </is>
+      </c>
+      <c r="P198" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>n.generic.title</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>Titolo per i giorni futuri (passi non ancora noti).</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>≤ 30</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>È ora del tappeto?</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Time for the treadmill?</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>¿Hora de la cinta de correr?</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>L’heure du tapis de course ?</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>Zeit fürs Laufband?</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>Hora da esteira?</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>トレッドミルの時間？</t>
+        </is>
+      </c>
+      <c r="M199" s="6" t="inlineStr">
+        <is>
+          <t>러닝머신 탈 시간인가요?</t>
+        </is>
+      </c>
+      <c r="N199" s="6" t="inlineStr">
+        <is>
+          <t>该上跑步机了吗？</t>
+        </is>
+      </c>
+      <c r="O199" s="6" t="inlineStr">
+        <is>
+          <t>該上跑步機了嗎？</t>
+        </is>
+      </c>
+      <c r="P199" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>n.generic.body</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Notifica serale</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>Notifica</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Corpo per i giorni futuri.</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>≤ 80</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>Apri NEAT per vedere quanti minuti ti servono stasera.</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Open NEAT to see how many minutes you need tonight.</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>Abre NEAT para ver cuántos minutos necesitas esta noche.</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>Ouvre NEAT pour voir combien de minutes il te faut ce soir.</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>Öffne NEAT und sieh, wie viele Minuten du heute Abend brauchst.</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>Abra o NEAT para ver quantos minutos você precisa esta noite.</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t>NEATを開いて、今夜あと何分必要か見てみよう。</t>
+        </is>
+      </c>
+      <c r="M200" s="6" t="inlineStr">
+        <is>
+          <t>NEAT를 열어 오늘 저녁 몇 분이 필요한지 확인해 보세요.</t>
+        </is>
+      </c>
+      <c r="N200" s="6" t="inlineStr">
+        <is>
+          <t>打开NEAT，看看今晚还需要多少分钟。</t>
+        </is>
+      </c>
+      <c r="O200" s="6" t="inlineStr">
+        <is>
+          <t>打開NEAT，看看今晚還需要幾分鐘。</t>
+        </is>
+      </c>
+      <c r="P200" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>p.health.read</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>Permessi (finestre di iOS)</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>Testo che iOS mostra quando l'app chiede di leggere da Salute. Tono formale-chiaro, è anche controllato da Apple.</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>≤ 250</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>NEAT legge i tuoi passi di oggi per calcolare quanti minuti di tappeto ti servono, e i tuoi allenamenti di camminata e corsa (passi, distanza, durata) per tarare la cadenza. Non scrive nulla e non invia dati fuori dal telefono.</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT reads today's steps to calculate the treadmill minutes you need, and your walking and running workouts (steps, distance, duration) to calibrate your cadence. It writes nothing and sends no data off your phone.</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT lee tus pasos de hoy para calcular los minutos de cinta de correr que necesitas, y tus entrenamientos de caminata y carrera (pasos, distancia, duración) para calibrar tu cadencia. No escribe nada ni envía datos fuera del teléfono.</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT lit tes pas du jour pour calculer les minutes nécessaires sur tapis de course et tes entraînements de marche et de course (pas, distance, durée) pour calibrer ta cadence. Aucune écriture ni envoi de données hors du téléphone.</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT liest heutige Schritte für die nötigen Laufbandminuten und deine Geh- und Lauftrainings (Schritte, Strecke, Dauer) zur Kalibrierung deiner Schrittfrequenz. Schreibt nichts und sendet keine Daten vom Handy.</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>O NEAT lê seus passos de hoje para calcular os minutos de esteira necessários e seus exercícios de caminhada e corrida (passos, distância, duração) para calibrar sua cadência. Não grava nada nem envia dados para fora do celular.</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>NEATは今日の歩数を読み取り、トレッドミルで必要な時間を計算します。また、ウォーキングとランニングのワークアウト（歩数、距離、時間）を読み取り、計算に使う1分あたりの歩数を調整します。データの書き込みやスマホ外への送信は行いません。</t>
+        </is>
+      </c>
+      <c r="M201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT는 오늘 걸음 수를 읽어 러닝머신에서 필요한 시간을 계산하고, 걷기와 달리기 운동 기록(걸음 수, 거리, 시간)을 읽어 계산에 쓰는 분당 걸음 수를 보정합니다. 데이터를 쓰거나 휴대폰 밖으로 보내지 않습니다.</t>
+        </is>
+      </c>
+      <c r="N201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT读取今日步数，计算所需的跑步机运动分钟数，并读取你的步行和跑步体能训练（步数、距离、时长）以校准步频。不写入任何内容，也不向手机外发送数据。</t>
+        </is>
+      </c>
+      <c r="O201" s="6" t="inlineStr">
+        <is>
+          <t>NEAT讀取今日步數，計算所需的跑步機運動分鐘數，並讀取你的步行和跑步體能訓練（步數、距離、時間長度）以校正步頻。不寫入任何內容，也不向手機外傳送資料。</t>
+        </is>
+      </c>
+      <c r="P201" s="6" t="inlineStr">
+        <is>
+          <t>Permesso: mantenuti passi di oggi, minuti sul tapis roulant, allenamenti di camminata/corsa, passi/distanza/durata per tarare la cadenza, nessuna scrittura o invio dal telefono. JA/KO spiegano la cadenza come passi al minuto. Revisione madrelingua consigliata per JA/KO/ZH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>p.health.write</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Permessi (finestre di iOS)</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>Testo obbligatorio per Apple anche se l'app non scrive.</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>≤ 200</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>NEAT non scrive nulla in Salute: si limita a leggere i dati. Questa dichiarazione è richiesta da Apple per le app con accesso a Salute.</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT writes nothing to Health: it only reads data. Apple requires this statement for apps with Health access.</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT no escribe nada en Salud: solo lee datos. Apple exige esta declaración para las apps con acceso a Salud.</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT n’écrit rien dans Santé : l’app se contente de lire les données. Apple exige cette déclaration pour les apps ayant accès à Santé.</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT schreibt nichts in Health, sondern liest nur Daten. Apple verlangt diese Erklärung für Apps mit Health-Zugriff.</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>O NEAT não grava nada no Saúde: apenas lê dados. A Apple exige esta declaração para apps com acesso ao Saúde.</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr">
+        <is>
+          <t>NEATはヘルスケアへの書き込みは行わず、データの読み取りのみを行います。この説明は、ヘルスケアにアクセスするアプリにAppleが義務付けているものです。</t>
+        </is>
+      </c>
+      <c r="M202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT는 건강 앱에 아무것도 쓰지 않고 데이터를 읽기만 합니다. Apple은 건강 앱에 접근하는 앱에 이 설명을 요구합니다.</t>
+        </is>
+      </c>
+      <c r="N202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT不向“健康”写入任何内容，只读取数据。Apple要求访问“健康”的App提供此声明。</t>
+        </is>
+      </c>
+      <c r="O202" s="6" t="inlineStr">
+        <is>
+          <t>NEAT不向「健康」寫入任何內容，只讀取資料。Apple要求存取「健康」的App提供此聲明。</t>
+        </is>
+      </c>
+      <c r="P202" s="6" t="inlineStr">
+        <is>
+          <t>Traduzione fedele: l’originale dice soltanto i passi, mentre p.health.read include anche gli allenamenti. Verificare la coerenza dell’italiano prima della pubblicazione; non corretto unilateralmente il testo di partenza. | COORDINAMENTO: italiano corretto («legge soltanto i tuoi passi» era inesatto: legge anche allenamenti e distanza) e traduzioni allineate. Da riportare nell'Info.plist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
           <t>p.health.widget</t>
         </is>
       </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="B203" s="5" t="inlineStr">
         <is>
           <t>Permessi (finestre di iOS)</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
+      <c r="C203" s="5" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>Lo stesso, per il widget.</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E203" s="5" t="inlineStr">
         <is>
           <t>≤ 200</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>Il widget legge i tuoi passi di oggi da Salute per mostrarli e per stimare i minuti a piedi che mancano. Non scrive nulla e non invia dati fuori dal telefono.</t>
         </is>
       </c>
-      <c r="G192" s="6" t="inlineStr">
+      <c r="G203" s="6" t="inlineStr">
         <is>
           <t>The widget reads today's steps from Health to display them and estimate the walking minutes left. It writes nothing and sends no data off your phone.</t>
         </is>
       </c>
-      <c r="H192" s="6" t="inlineStr">
+      <c r="H203" s="6" t="inlineStr">
         <is>
           <t>El widget lee tus pasos de hoy de Salud para mostrarlos y estimar los minutos que te quedan andando. No escribe nada ni envía datos fuera del teléfono.</t>
         </is>
       </c>
-      <c r="I192" s="6" t="inlineStr">
+      <c r="I203" s="6" t="inlineStr">
         <is>
           <t>Le widget lit tes pas du jour dans Santé pour les afficher et estimer les minutes de marche restantes. Aucune écriture ni envoi de données hors du téléphone.</t>
         </is>
       </c>
-      <c r="J192" s="6" t="inlineStr">
+      <c r="J203" s="6" t="inlineStr">
         <is>
           <t>Das Widget liest heutige Schritte aus Health, um sie anzuzeigen und die übrigen Gehminuten zu schätzen. Schreibt nichts und sendet keine Daten vom Handy.</t>
         </is>
       </c>
-      <c r="K192" s="6" t="inlineStr">
+      <c r="K203" s="6" t="inlineStr">
         <is>
           <t>O widget lê seus passos de hoje no Saúde para mostrá-los e estimar os minutos de caminhada restantes. Não grava nada nem envia dados para fora do celular.</t>
         </is>
       </c>
-      <c r="L192" s="6" t="inlineStr">
+      <c r="L203" s="6" t="inlineStr">
         <is>
           <t>ウィジェットはヘルスケアから今日の歩数を読み取って表示し、あと何分歩く必要があるかを推定します。データの書き込みやスマホ外への送信は行いません。</t>
         </is>
       </c>
-      <c r="M192" s="6" t="inlineStr">
+      <c r="M203" s="6" t="inlineStr">
         <is>
           <t>위젯은 건강 앱에서 오늘 걸음 수를 읽어 표시하고, 더 걸어야 할 시간을 추정합니다. 데이터를 쓰거나 휴대폰 밖으로 보내지 않습니다.</t>
         </is>
       </c>
-      <c r="N192" s="6" t="inlineStr">
+      <c r="N203" s="6" t="inlineStr">
         <is>
           <t>小组件从“健康”读取今日步数，用于显示步数并估算还需步行的分钟数。不写入任何内容，也不向手机外发送数据。</t>
         </is>
       </c>
-      <c r="O192" s="6" t="inlineStr">
+      <c r="O203" s="6" t="inlineStr">
         <is>
           <t>小工具從「健康」讀取今日步數，用於顯示步數並估算還需步行的分鐘數。不寫入任何內容，也不向手機外傳送資料。</t>
         </is>
       </c>
-      <c r="P192" s="6" t="inlineStr">
+      <c r="P203" s="6" t="inlineStr">
         <is>
           <t>ZH-Hans: 小组件; ZH-Hant Taiwan: 小工具. Non aggiunte promesse ulteriori. Revisione madrelingua consigliata per i testi di permesso JA/KO/ZH.</t>
         </is>

--- a/ios/localizzazione/NEAT_testi_tradotti.xlsx
+++ b/ios/localizzazione/NEAT_testi_tradotti.xlsx
@@ -1473,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P203"/>
+  <dimension ref="A1:P207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18120,6 +18120,334 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>w.watch.gallery.desc</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>Descrizione delle complicazioni nella scelta del quadrante dell'Apple Watch (al posto di w.gallery.desc, che parla del blocco schermo).</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>≤ 70</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Passi, minuti che mancano e serie, sul quadrante.</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Steps, minutes left and your streak, right on your watch face.</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>Pasos, minutos restantes y racha, en la esfera del reloj.</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>Pas, minutes restantes et série, sur le cadran.</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>Schritte, übrige Minuten und Serie, direkt auf dem Zifferblatt.</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>Passos, minutos restantes e sequência, no mostrador do relógio.</t>
+        </is>
+      </c>
+      <c r="L204" s="6" t="inlineStr">
+        <is>
+          <t>歩数、残り時間、連続記録を文字盤でチェック。</t>
+        </is>
+      </c>
+      <c r="M204" s="6" t="inlineStr">
+        <is>
+          <t>시계 페이스에서 걸음 수, 남은 시간, 연속 기록을 확인해요.</t>
+        </is>
+      </c>
+      <c r="N204" s="6" t="inlineStr">
+        <is>
+          <t>步数、剩余分钟数和连续记录，表盘上就能看。</t>
+        </is>
+      </c>
+      <c r="O204" s="6" t="inlineStr">
+        <is>
+          <t>步數、剩餘分鐘數和連續紀錄，錶面上就能看。</t>
+        </is>
+      </c>
+      <c r="P204" s="6" t="inlineStr">
+        <is>
+          <t>Bozza di Claude (1.2), da confermare con ChatGPT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>w.watch.nodata</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>Visibile</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>App per Apple Watch: riga sotto la barra quando Salute non dà passi (permesso negato o nessun dato), al posto dei minuti che mancano, MAIUSCOLO.</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>≤ 22</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>NIENTE DATI DA SALUTE</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>NO HEALTH DATA</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>SIN DATOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>PAS DE DONNÉES SANTÉ</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>KEINE HEALTH-DATEN</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>SEM DADOS DO SAÚDE</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr">
+        <is>
+          <t>ヘルスケアのデータなし</t>
+        </is>
+      </c>
+      <c r="M205" s="6" t="inlineStr">
+        <is>
+          <t>건강 데이터 없음</t>
+        </is>
+      </c>
+      <c r="N205" s="6" t="inlineStr">
+        <is>
+          <t>无“健康”数据</t>
+        </is>
+      </c>
+      <c r="O205" s="6" t="inlineStr">
+        <is>
+          <t>無「健康」資料</t>
+        </is>
+      </c>
+      <c r="P205" s="6" t="inlineStr">
+        <is>
+          <t>Bozza di Claude (1.2), da confermare con ChatGPT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>w.watch.nodata.vo</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>VoiceOver</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>Descrizione letta ad alta voce nello stesso caso: dice dove controllare il permesso.</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Nessun dato da Salute. Controlla i permessi di NEAT nell'app Salute del telefono.</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>No data from Health. Check NEAT's permissions in the Health app on your iPhone.</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>No hay datos de Salud. Revisa los permisos de NEAT en la app Salud del iPhone.</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>Aucune donnée de Santé. Vérifie les autorisations de NEAT dans l’app Santé de l’iPhone.</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>Keine Daten aus Health. Prüfe die Berechtigungen von NEAT in der Health-App auf dem iPhone.</t>
+        </is>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>Sem dados do Saúde. Verifique as permissões do NEAT no app Saúde do iPhone.</t>
+        </is>
+      </c>
+      <c r="L206" s="6" t="inlineStr">
+        <is>
+          <t>ヘルスケアのデータがありません。iPhoneのヘルスケアアプリでNEATのアクセス権を確認してください。</t>
+        </is>
+      </c>
+      <c r="M206" s="6" t="inlineStr">
+        <is>
+          <t>건강 앱 데이터가 없어요. iPhone의 건강 앱에서 NEAT의 권한을 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="N206" s="6" t="inlineStr">
+        <is>
+          <t>没有来自“健康”的数据。请在 iPhone 的“健康”App 中检查 NEAT 的权限。</t>
+        </is>
+      </c>
+      <c r="O206" s="6" t="inlineStr">
+        <is>
+          <t>沒有來自「健康」的資料。請在 iPhone 的「健康」App 中檢查 NEAT 的權限。</t>
+        </is>
+      </c>
+      <c r="P206" s="6" t="inlineStr">
+        <is>
+          <t>Bozza di Claude (1.2), da confermare con ChatGPT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>p.health.watch</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Permessi (finestre di watchOS)</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>Testo mostrato quando l'app per Apple Watch chiede di leggere i passi da Salute. Tono formale-chiaro, controllato da Apple.</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>≤ 200</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>NEAT legge i tuoi passi di oggi da Salute per mostrarli sull'orologio e stimare i minuti che mancano. Non scrive nulla e non invia dati fuori dall'orologio.</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT reads today's steps from Health to show them on your watch and estimate the minutes left. It writes nothing and sends no data off your watch.</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT lee tus pasos de hoy de Salud para mostrarlos en el reloj y estimar los minutos que faltan. No escribe nada ni envía datos fuera del reloj.</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT lit tes pas du jour dans Santé pour les afficher sur la montre et estimer les minutes restantes. Aucune écriture ni envoi de données hors de la montre.</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT liest heutige Schritte aus Health, um sie auf der Uhr anzuzeigen und die übrigen Minuten zu schätzen. Schreibt nichts und sendet keine Daten von der Uhr.</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>O NEAT lê seus passos de hoje no Saúde para mostrá-los no relógio e estimar os minutos restantes. Não grava nada nem envia dados para fora do relógio.</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>NEATはヘルスケアから今日の歩数を読み取ってApple Watchに表示し、残りの時間を推定します。データの書き込みや外部への送信は行いません。</t>
+        </is>
+      </c>
+      <c r="M207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT는 건강 앱에서 오늘 걸음 수를 읽어 시계에 표시하고 남은 시간을 추정합니다. 데이터를 쓰거나 시계 밖으로 보내지 않습니다.</t>
+        </is>
+      </c>
+      <c r="N207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT从“健康”读取今日步数，在手表上显示并估算剩余分钟数。不写入任何内容，也不向手表外发送数据。</t>
+        </is>
+      </c>
+      <c r="O207" s="6" t="inlineStr">
+        <is>
+          <t>NEAT從「健康」讀取今日步數，在手錶上顯示並估算剩餘分鐘數。不寫入任何內容，也不向手錶外傳送資料。</t>
+        </is>
+      </c>
+      <c r="P207" s="6" t="inlineStr">
+        <is>
+          <t>Bozza di Claude (1.2), da confermare con ChatGPT.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ios/localizzazione/NEAT_testi_tradotti.xlsx
+++ b/ios/localizzazione/NEAT_testi_tradotti.xlsx
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Pagina 2. Paragrafo: rassicurazione sulla privacy.</t>
+          <t>Pagina 2. Paragrafo: rassicurazione sulla privacy. «account» = l'account Apple dell'utente (iCloud), non un account di NEAT, che non esiste.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2096,57 +2096,57 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Non scrive niente e nessun dato esce dal telefono.</t>
+          <t>I tuoi dati non lasciano mai il tuo account.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>It writes nothing. No data leaves your phone.</t>
+          <t>Your data never leaves your account.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>No escribe nada y ningún dato sale del teléfono.</t>
+          <t>Tus datos nunca salen de tu cuenta.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>L’app n’écrit rien. Aucune donnée ne quitte ton téléphone.</t>
+          <t>Tes données ne quittent jamais ton compte.</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Schreibt nichts. Keine Daten verlassen dein Handy.</t>
+          <t>Deine Daten verlassen nie deinen Account.</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Não grava nada. Nenhum dado sai do celular.</t>
+          <t>Seus dados nunca saem da sua conta.</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>書き込みはせず、データはスマホの外に送らないよ。</t>
+          <t>データがあなたのアカウントの外に出ることはないよ。</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>아무것도 쓰지 않고, 데이터를 휴대폰 밖으로 보내지 않아요.</t>
+          <t>데이터는 내 계정 밖으로 나가지 않아요.</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>不写入任何内容，也不向手机外发送数据。</t>
+          <t>你的数据从不离开你的账户。</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>不寫入任何內容，也不向手機外傳送資料。</t>
+          <t>你的資料絕不會離開你的帳號。</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bozza di Claude (1.1), da confermare con ChatGPT. Prima: «Non scrive niente e nessun dato esce dal telefono.»</t>
         </is>
       </c>
     </row>

--- a/ios/localizzazione/NEAT_testi_tradotti.xlsx
+++ b/ios/localizzazione/NEAT_testi_tradotti.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>I tuoi dati non lasciano mai il tuo account.</t>
+          <t>I tuoi dati non lasciano mai il tuo account Apple.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
